--- a/docs/qa/3기리포트_QA_TC_20261012.xlsx
+++ b/docs/qa/3기리포트_QA_TC_20261012.xlsx
@@ -10,16 +10,18 @@
     <sheet name="요약" sheetId="1" state="visible" r:id="rId1"/>
     <sheet name="TC" sheetId="2" state="visible" r:id="rId2"/>
     <sheet name="결함" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="결정 필요" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="데이터 요청" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet name="계정 · 안내" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet name="스크린샷" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet name="피그마 정리" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="결정 필요" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="데이터 요청" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="계정 · 안내" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet name="스크린샷" sheetId="8" state="visible" r:id="rId8"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'TC'!$A$1:$T$1</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'결함'!$A$1:$N$1</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'결정 필요'!$A$1:$H$1</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'데이터 요청'!$A$1:$G$1</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'피그마 정리'!$A$1:$H$1</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'결정 필요'!$A$1:$H$1</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'데이터 요청'!$A$1:$G$1</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -144,12 +146,12 @@
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
@@ -274,7 +276,7 @@
       <row>4</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="3810000" cy="4114800"/>
+    <ext cx="4000500" cy="4448175"/>
     <pic>
       <nvPicPr>
         <cNvPr id="1" name="Image 1" descr="Picture"/>
@@ -294,12 +296,12 @@
   </oneCellAnchor>
   <oneCellAnchor>
     <from>
-      <col>6</col>
+      <col>7</col>
       <colOff>0</colOff>
       <row>4</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="3810000" cy="4114800"/>
+    <ext cx="4000500" cy="4448175"/>
     <pic>
       <nvPicPr>
         <cNvPr id="2" name="Image 2" descr="Picture"/>
@@ -321,10 +323,10 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>36</row>
+      <row>34</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="2095500" cy="4305300"/>
+    <ext cx="4000500" cy="4448175"/>
     <pic>
       <nvPicPr>
         <cNvPr id="3" name="Image 3" descr="Picture"/>
@@ -344,12 +346,12 @@
   </oneCellAnchor>
   <oneCellAnchor>
     <from>
-      <col>4</col>
+      <col>7</col>
       <colOff>0</colOff>
-      <row>36</row>
+      <row>34</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="2095500" cy="4305300"/>
+    <ext cx="4000500" cy="4505325"/>
     <pic>
       <nvPicPr>
         <cNvPr id="4" name="Image 4" descr="Picture"/>
@@ -369,12 +371,12 @@
   </oneCellAnchor>
   <oneCellAnchor>
     <from>
-      <col>8</col>
+      <col>0</col>
       <colOff>0</colOff>
-      <row>36</row>
+      <row>64</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="2095500" cy="4305300"/>
+    <ext cx="4000500" cy="5057775"/>
     <pic>
       <nvPicPr>
         <cNvPr id="5" name="Image 5" descr="Picture"/>
@@ -394,12 +396,12 @@
   </oneCellAnchor>
   <oneCellAnchor>
     <from>
-      <col>12</col>
+      <col>7</col>
       <colOff>0</colOff>
-      <row>36</row>
+      <row>64</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="2095500" cy="4305300"/>
+    <ext cx="4000500" cy="4762500"/>
     <pic>
       <nvPicPr>
         <cNvPr id="6" name="Image 6" descr="Picture"/>
@@ -419,12 +421,12 @@
   </oneCellAnchor>
   <oneCellAnchor>
     <from>
-      <col>16</col>
+      <col>0</col>
       <colOff>0</colOff>
-      <row>36</row>
+      <row>94</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="2095500" cy="4305300"/>
+    <ext cx="4000500" cy="4886325"/>
     <pic>
       <nvPicPr>
         <cNvPr id="7" name="Image 7" descr="Picture"/>
@@ -444,12 +446,12 @@
   </oneCellAnchor>
   <oneCellAnchor>
     <from>
-      <col>0</col>
+      <col>7</col>
       <colOff>0</colOff>
-      <row>68</row>
+      <row>94</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="2095500" cy="4533900"/>
+    <ext cx="4000500" cy="4448175"/>
     <pic>
       <nvPicPr>
         <cNvPr id="8" name="Image 8" descr="Picture"/>
@@ -469,12 +471,12 @@
   </oneCellAnchor>
   <oneCellAnchor>
     <from>
-      <col>4</col>
+      <col>0</col>
       <colOff>0</colOff>
-      <row>68</row>
+      <row>124</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="2095500" cy="4305300"/>
+    <ext cx="4000500" cy="4448175"/>
     <pic>
       <nvPicPr>
         <cNvPr id="9" name="Image 9" descr="Picture"/>
@@ -494,12 +496,12 @@
   </oneCellAnchor>
   <oneCellAnchor>
     <from>
-      <col>8</col>
+      <col>7</col>
       <colOff>0</colOff>
-      <row>68</row>
+      <row>124</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="2095500" cy="4533900"/>
+    <ext cx="4000500" cy="4448175"/>
     <pic>
       <nvPicPr>
         <cNvPr id="10" name="Image 10" descr="Picture"/>
@@ -519,12 +521,12 @@
   </oneCellAnchor>
   <oneCellAnchor>
     <from>
-      <col>12</col>
+      <col>0</col>
       <colOff>0</colOff>
-      <row>68</row>
+      <row>154</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="2095500" cy="10096500"/>
+    <ext cx="4000500" cy="4448175"/>
     <pic>
       <nvPicPr>
         <cNvPr id="11" name="Image 11" descr="Picture"/>
@@ -544,12 +546,12 @@
   </oneCellAnchor>
   <oneCellAnchor>
     <from>
-      <col>16</col>
+      <col>7</col>
       <colOff>0</colOff>
-      <row>68</row>
+      <row>154</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="2095500" cy="4533900"/>
+    <ext cx="4000500" cy="4448175"/>
     <pic>
       <nvPicPr>
         <cNvPr id="12" name="Image 12" descr="Picture"/>
@@ -557,6 +559,106 @@
       </nvPicPr>
       <blipFill>
         <a:blip cstate="print" r:embed="rId12"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>0</col>
+      <colOff>0</colOff>
+      <row>184</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="4000500" cy="4448175"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="13" name="Image 13" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId13"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>7</col>
+      <colOff>0</colOff>
+      <row>184</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="4000500" cy="4448175"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="14" name="Image 14" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId14"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>0</col>
+      <colOff>0</colOff>
+      <row>214</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="2095500" cy="4533900"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="15" name="Image 15" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId15"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>7</col>
+      <colOff>0</colOff>
+      <row>214</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="2095500" cy="4533900"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="16" name="Image 16" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId16"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -882,7 +984,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>TC 시트의 결과 칸을 채우면 아래 숫자가 자동으로 바뀝니다. 배포 판단: P1에 실패가 하나라도 있으면 배포 불가.</t>
+          <t>QA 기준 = 피그마(목업 + 디스크립션, 페이지 1028:3313). TC 시트의 결과 칸을 채우면 아래 숫자가 자동으로 바뀝니다. 배포 판단: P1에 실패가 하나라도 있으면 배포 불가.</t>
         </is>
       </c>
     </row>
@@ -1092,6 +1194,11 @@
           <t>결함</t>
         </is>
       </c>
+      <c r="D13" s="8" t="inlineStr">
+        <is>
+          <t>피그마 정리</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="3" t="inlineStr">
@@ -1109,18 +1216,27 @@
           <t>해결</t>
         </is>
       </c>
+      <c r="D14" s="3" t="inlineStr">
+        <is>
+          <t>건수</t>
+        </is>
+      </c>
     </row>
     <row r="15">
-      <c r="A15" s="4">
+      <c r="A15" s="10">
         <f>COUNTIF(결함!$A$2:$A$60,"BUG-*")</f>
         <v/>
       </c>
-      <c r="B15" s="4">
+      <c r="B15" s="10">
         <f>A15-C15</f>
         <v/>
       </c>
-      <c r="C15" s="4">
+      <c r="C15" s="10">
         <f>COUNTIF(결함!$E$2:$E$60,"해결")</f>
+        <v/>
+      </c>
+      <c r="D15" s="4">
+        <f>COUNTIF('피그마 정리'!$A$2:$A$40,"FIG-*")</f>
         <v/>
       </c>
     </row>
@@ -1170,16 +1286,16 @@
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="10" t="n"/>
-      <c r="B22" s="11" t="inlineStr">
+      <c r="A22" s="11" t="n"/>
+      <c r="B22" s="12" t="inlineStr">
         <is>
           <t>노란 칸 = 직접 입력 (결과 · 실제 결과 · 결함 ID · 증빙 · 테스터 · 날짜 · 결정)</t>
         </is>
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="12" t="n"/>
-      <c r="B23" s="11" t="inlineStr">
+      <c r="A23" s="13" t="n"/>
+      <c r="B23" s="12" t="inlineStr">
         <is>
           <t>초록 칸 = 기획이 웹 샘플로 먼저 본 결과 (10/12). 앱에서 다시 확인해 N · O열에 적어 주세요</t>
         </is>
@@ -1334,49 +1450,49 @@
           <t>P1</t>
         </is>
       </c>
-      <c r="C2" s="13" t="inlineStr">
+      <c r="C2" s="10" t="inlineStr">
         <is>
           <t>1 진입</t>
         </is>
       </c>
-      <c r="D2" s="13" t="inlineStr">
+      <c r="D2" s="10" t="inlineStr">
         <is>
           <t>체험 홈</t>
         </is>
       </c>
-      <c r="E2" s="13" t="inlineStr">
+      <c r="E2" s="10" t="inlineStr">
         <is>
           <t>①</t>
         </is>
       </c>
-      <c r="F2" s="13" t="inlineStr">
+      <c r="F2" s="10" t="inlineStr">
         <is>
           <t>앱</t>
         </is>
       </c>
-      <c r="G2" s="13" t="inlineStr">
+      <c r="G2" s="10" t="inlineStr">
         <is>
           <t>dev 빌드 설치 · 로그인</t>
         </is>
       </c>
-      <c r="H2" s="13" t="inlineStr">
+      <c r="H2" s="10" t="inlineStr">
         <is>
           <t>체험 홈으로 들어간다</t>
         </is>
       </c>
-      <c r="I2" s="13" t="inlineStr">
+      <c r="I2" s="10" t="inlineStr">
         <is>
           <t>상단에 3기 리포트 카드(전용 배너 이미지)가 보인다</t>
         </is>
       </c>
-      <c r="J2" s="13" t="inlineStr">
+      <c r="J2" s="10" t="inlineStr">
         <is>
           <t>B-01 · IA-R-08</t>
         </is>
       </c>
-      <c r="K2" s="13" t="n"/>
+      <c r="K2" s="10" t="n"/>
       <c r="L2" s="4" t="n"/>
-      <c r="M2" s="13" t="n"/>
+      <c r="M2" s="10" t="n"/>
       <c r="N2" s="14" t="inlineStr">
         <is>
           <t>미실행</t>
@@ -1400,53 +1516,53 @@
           <t>P1</t>
         </is>
       </c>
-      <c r="C3" s="13" t="inlineStr">
+      <c r="C3" s="10" t="inlineStr">
         <is>
           <t>1 진입</t>
         </is>
       </c>
-      <c r="D3" s="13" t="inlineStr">
+      <c r="D3" s="10" t="inlineStr">
         <is>
           <t>자동 팝업</t>
         </is>
       </c>
-      <c r="E3" s="13" t="inlineStr">
+      <c r="E3" s="10" t="inlineStr">
         <is>
           <t>①</t>
         </is>
       </c>
-      <c r="F3" s="13" t="inlineStr">
+      <c r="F3" s="10" t="inlineStr">
         <is>
           <t>앱</t>
         </is>
       </c>
-      <c r="G3" s="13" t="inlineStr">
+      <c r="G3" s="10" t="inlineStr">
         <is>
           <t>리포트를 한 번도 열지 않은 상태</t>
         </is>
       </c>
-      <c r="H3" s="13" t="inlineStr">
+      <c r="H3" s="10" t="inlineStr">
         <is>
           <t>로그인 직후 홈 진입</t>
         </is>
       </c>
-      <c r="I3" s="13" t="inlineStr">
+      <c r="I3" s="10" t="inlineStr">
         <is>
           <t>리포트가 자동으로 1회 열리고 표지(SC-RP-01)부터 보인다</t>
         </is>
       </c>
-      <c r="J3" s="13" t="inlineStr">
+      <c r="J3" s="10" t="inlineStr">
         <is>
           <t>IA-R-01</t>
         </is>
       </c>
       <c r="K3" s="16" t="inlineStr">
         <is>
-          <t>dev_01_cover.png</t>
+          <t>cmp_01.png</t>
         </is>
       </c>
       <c r="L3" s="4" t="n"/>
-      <c r="M3" s="13" t="n"/>
+      <c r="M3" s="10" t="n"/>
       <c r="N3" s="14" t="inlineStr">
         <is>
           <t>미실행</t>
@@ -1470,49 +1586,49 @@
           <t>P2</t>
         </is>
       </c>
-      <c r="C4" s="13" t="inlineStr">
+      <c r="C4" s="10" t="inlineStr">
         <is>
           <t>1 진입</t>
         </is>
       </c>
-      <c r="D4" s="13" t="inlineStr">
+      <c r="D4" s="10" t="inlineStr">
         <is>
           <t>자동 팝업</t>
         </is>
       </c>
-      <c r="E4" s="13" t="inlineStr">
+      <c r="E4" s="10" t="inlineStr">
         <is>
           <t>①</t>
         </is>
       </c>
-      <c r="F4" s="13" t="inlineStr">
+      <c r="F4" s="10" t="inlineStr">
         <is>
           <t>앱</t>
         </is>
       </c>
-      <c r="G4" s="13" t="inlineStr">
+      <c r="G4" s="10" t="inlineStr">
         <is>
           <t>E-02 이후</t>
         </is>
       </c>
-      <c r="H4" s="13" t="inlineStr">
+      <c r="H4" s="10" t="inlineStr">
         <is>
           <t>리포트를 닫고 앱을 껐다 다시 연다</t>
         </is>
       </c>
-      <c r="I4" s="13" t="inlineStr">
+      <c r="I4" s="10" t="inlineStr">
         <is>
           <t>자동 팝업이 다시 뜨지 않는다 · 홈 카드는 그대로 있다</t>
         </is>
       </c>
-      <c r="J4" s="13" t="inlineStr">
+      <c r="J4" s="10" t="inlineStr">
         <is>
           <t>IA-R-01</t>
         </is>
       </c>
-      <c r="K4" s="13" t="n"/>
+      <c r="K4" s="10" t="n"/>
       <c r="L4" s="4" t="n"/>
-      <c r="M4" s="13" t="n"/>
+      <c r="M4" s="10" t="n"/>
       <c r="N4" s="14" t="inlineStr">
         <is>
           <t>미실행</t>
@@ -1536,49 +1652,49 @@
           <t>P1</t>
         </is>
       </c>
-      <c r="C5" s="13" t="inlineStr">
+      <c r="C5" s="10" t="inlineStr">
         <is>
           <t>1 진입</t>
         </is>
       </c>
-      <c r="D5" s="13" t="inlineStr">
+      <c r="D5" s="10" t="inlineStr">
         <is>
           <t>홈 카드</t>
         </is>
       </c>
-      <c r="E5" s="13" t="inlineStr">
+      <c r="E5" s="10" t="inlineStr">
         <is>
           <t>①</t>
         </is>
       </c>
-      <c r="F5" s="13" t="inlineStr">
+      <c r="F5" s="10" t="inlineStr">
         <is>
           <t>앱</t>
         </is>
       </c>
-      <c r="G5" s="13" t="inlineStr">
+      <c r="G5" s="10" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="H5" s="13" t="inlineStr">
+      <c r="H5" s="10" t="inlineStr">
         <is>
           <t>홈 카드를 누른다</t>
         </is>
       </c>
-      <c r="I5" s="13" t="inlineStr">
+      <c r="I5" s="10" t="inlineStr">
         <is>
           <t>리포트가 표지부터 열린다</t>
         </is>
       </c>
-      <c r="J5" s="13" t="inlineStr">
+      <c r="J5" s="10" t="inlineStr">
         <is>
           <t>IA-R-03</t>
         </is>
       </c>
-      <c r="K5" s="13" t="n"/>
+      <c r="K5" s="10" t="n"/>
       <c r="L5" s="4" t="n"/>
-      <c r="M5" s="13" t="n"/>
+      <c r="M5" s="10" t="n"/>
       <c r="N5" s="14" t="inlineStr">
         <is>
           <t>미실행</t>
@@ -1602,49 +1718,49 @@
           <t>P1</t>
         </is>
       </c>
-      <c r="C6" s="13" t="inlineStr">
+      <c r="C6" s="10" t="inlineStr">
         <is>
           <t>1 진입</t>
         </is>
       </c>
-      <c r="D6" s="13" t="inlineStr">
+      <c r="D6" s="10" t="inlineStr">
         <is>
           <t>진행 내역</t>
         </is>
       </c>
-      <c r="E6" s="13" t="inlineStr">
+      <c r="E6" s="10" t="inlineStr">
         <is>
           <t>①</t>
         </is>
       </c>
-      <c r="F6" s="13" t="inlineStr">
+      <c r="F6" s="10" t="inlineStr">
         <is>
           <t>앱</t>
         </is>
       </c>
-      <c r="G6" s="13" t="inlineStr">
+      <c r="G6" s="10" t="inlineStr">
         <is>
           <t>10/20 제출 빌드</t>
         </is>
       </c>
-      <c r="H6" s="13" t="inlineStr">
+      <c r="H6" s="10" t="inlineStr">
         <is>
           <t>내 정보 &gt; 프로그램 진행 내역 &gt; 3기 항목을 누른다</t>
         </is>
       </c>
-      <c r="I6" s="13" t="inlineStr">
+      <c r="I6" s="10" t="inlineStr">
         <is>
           <t>리포트가 표지부터 열린다</t>
         </is>
       </c>
-      <c r="J6" s="13" t="inlineStr">
+      <c r="J6" s="10" t="inlineStr">
         <is>
           <t>F4 · IA-R-07</t>
         </is>
       </c>
-      <c r="K6" s="13" t="n"/>
+      <c r="K6" s="10" t="n"/>
       <c r="L6" s="4" t="n"/>
-      <c r="M6" s="13" t="n"/>
+      <c r="M6" s="10" t="n"/>
       <c r="N6" s="14" t="inlineStr">
         <is>
           <t>미실행</t>
@@ -1668,49 +1784,49 @@
           <t>P2</t>
         </is>
       </c>
-      <c r="C7" s="13" t="inlineStr">
+      <c r="C7" s="10" t="inlineStr">
         <is>
           <t>1 진입</t>
         </is>
       </c>
-      <c r="D7" s="13" t="inlineStr">
+      <c r="D7" s="10" t="inlineStr">
         <is>
           <t>체험 홈</t>
         </is>
       </c>
-      <c r="E7" s="13" t="inlineStr">
+      <c r="E7" s="10" t="inlineStr">
         <is>
           <t>⑤</t>
         </is>
       </c>
-      <c r="F7" s="13" t="inlineStr">
+      <c r="F7" s="10" t="inlineStr">
         <is>
           <t>앱</t>
         </is>
       </c>
-      <c r="G7" s="13" t="inlineStr">
+      <c r="G7" s="10" t="inlineStr">
         <is>
           <t>다른 프로그램 진행 중</t>
         </is>
       </c>
-      <c r="H7" s="13" t="inlineStr">
+      <c r="H7" s="10" t="inlineStr">
         <is>
           <t>홈으로 들어간다</t>
         </is>
       </c>
-      <c r="I7" s="13" t="inlineStr">
+      <c r="I7" s="10" t="inlineStr">
         <is>
           <t>리포트 카드가 없다</t>
         </is>
       </c>
-      <c r="J7" s="13" t="inlineStr">
+      <c r="J7" s="10" t="inlineStr">
         <is>
           <t>IA-R-08</t>
         </is>
       </c>
-      <c r="K7" s="13" t="n"/>
+      <c r="K7" s="10" t="n"/>
       <c r="L7" s="4" t="n"/>
-      <c r="M7" s="13" t="n"/>
+      <c r="M7" s="10" t="n"/>
       <c r="N7" s="14" t="inlineStr">
         <is>
           <t>미실행</t>
@@ -1734,49 +1850,49 @@
           <t>P2</t>
         </is>
       </c>
-      <c r="C8" s="13" t="inlineStr">
+      <c r="C8" s="10" t="inlineStr">
         <is>
           <t>1 진입</t>
         </is>
       </c>
-      <c r="D8" s="13" t="inlineStr">
+      <c r="D8" s="10" t="inlineStr">
         <is>
           <t>공개 전</t>
         </is>
       </c>
-      <c r="E8" s="13" t="inlineStr">
+      <c r="E8" s="10" t="inlineStr">
         <is>
           <t>⑥</t>
         </is>
       </c>
-      <c r="F8" s="13" t="inlineStr">
+      <c r="F8" s="10" t="inlineStr">
         <is>
           <t>앱</t>
         </is>
       </c>
-      <c r="G8" s="13" t="inlineStr">
+      <c r="G8" s="10" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="H8" s="13" t="inlineStr">
+      <c r="H8" s="10" t="inlineStr">
         <is>
           <t>홈 확인 후 리포트 링크로 직접 연다</t>
         </is>
       </c>
-      <c r="I8" s="13" t="inlineStr">
+      <c r="I8" s="10" t="inlineStr">
         <is>
           <t>카드 없음 · "아직 볼 수 없어요" 안내</t>
         </is>
       </c>
-      <c r="J8" s="13" t="inlineStr">
+      <c r="J8" s="10" t="inlineStr">
         <is>
           <t>P09</t>
         </is>
       </c>
-      <c r="K8" s="13" t="n"/>
+      <c r="K8" s="10" t="n"/>
       <c r="L8" s="4" t="n"/>
-      <c r="M8" s="13" t="n"/>
+      <c r="M8" s="10" t="n"/>
       <c r="N8" s="14" t="inlineStr">
         <is>
           <t>미실행</t>
@@ -1800,59 +1916,59 @@
           <t>P1</t>
         </is>
       </c>
-      <c r="C9" s="13" t="inlineStr">
+      <c r="C9" s="10" t="inlineStr">
         <is>
           <t>1 진입</t>
         </is>
       </c>
-      <c r="D9" s="13" t="inlineStr">
+      <c r="D9" s="10" t="inlineStr">
         <is>
           <t>비대상 P20</t>
         </is>
       </c>
-      <c r="E9" s="13" t="inlineStr">
+      <c r="E9" s="10" t="inlineStr">
         <is>
           <t>⑦</t>
         </is>
       </c>
-      <c r="F9" s="13" t="inlineStr">
+      <c r="F9" s="10" t="inlineStr">
         <is>
           <t>앱 · 웹</t>
         </is>
       </c>
-      <c r="G9" s="13" t="inlineStr">
+      <c r="G9" s="10" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="H9" s="13" t="inlineStr">
+      <c r="H9" s="10" t="inlineStr">
         <is>
           <t>리포트 링크로 직접 연다</t>
         </is>
       </c>
-      <c r="I9" s="13" t="inlineStr">
+      <c r="I9" s="10" t="inlineStr">
         <is>
           <t>제목 없이 본문 "2026년 인천 남동구 보건소 두뇌운동 치매 예방 교실 3기 참여자에게만 제공되는 리포트입니다. 자세한 문의는 인천 남동구 보건소로 문의 부탁드립니다." + [홈으로 돌아가기]</t>
         </is>
       </c>
-      <c r="J9" s="13" t="inlineStr">
+      <c r="J9" s="10" t="inlineStr">
         <is>
           <t>P20 · gate-nontarget</t>
         </is>
       </c>
       <c r="K9" s="16" t="inlineStr">
         <is>
-          <t>dev_P20.png</t>
+          <t>cmp_sys05.png</t>
         </is>
       </c>
       <c r="L9" s="17" t="inlineStr">
         <is>
-          <t>통과</t>
+          <t>실패</t>
         </is>
       </c>
       <c r="M9" s="18" t="inlineStr">
         <is>
-          <t>state=sys05 문구 일치</t>
+          <t>문구는 일치 · 아이콘 · 버튼 배치 다름 → BUG-07</t>
         </is>
       </c>
       <c r="N9" s="14" t="inlineStr">
@@ -1878,49 +1994,49 @@
           <t>P1</t>
         </is>
       </c>
-      <c r="C10" s="13" t="inlineStr">
+      <c r="C10" s="10" t="inlineStr">
         <is>
           <t>1 진입</t>
         </is>
       </c>
-      <c r="D10" s="13" t="inlineStr">
+      <c r="D10" s="10" t="inlineStr">
         <is>
           <t>강제 업데이트</t>
         </is>
       </c>
-      <c r="E10" s="13" t="inlineStr">
+      <c r="E10" s="10" t="inlineStr">
         <is>
           <t>아무 계정</t>
         </is>
       </c>
-      <c r="F10" s="13" t="inlineStr">
+      <c r="F10" s="10" t="inlineStr">
         <is>
           <t>앱</t>
         </is>
       </c>
-      <c r="G10" s="13" t="inlineStr">
+      <c r="G10" s="10" t="inlineStr">
         <is>
           <t>앱 4.1.0 이하 설치</t>
         </is>
       </c>
-      <c r="H10" s="13" t="inlineStr">
+      <c r="H10" s="10" t="inlineStr">
         <is>
           <t>앱을 연다</t>
         </is>
       </c>
-      <c r="I10" s="13" t="inlineStr">
+      <c r="I10" s="10" t="inlineStr">
         <is>
           <t>4.1.1 미만은 업데이트 안내 · 앱 사용 차단</t>
         </is>
       </c>
-      <c r="J10" s="13" t="inlineStr">
+      <c r="J10" s="10" t="inlineStr">
         <is>
           <t>K-15 · IA-R-13 · 개발 D-5</t>
         </is>
       </c>
-      <c r="K10" s="13" t="n"/>
+      <c r="K10" s="10" t="n"/>
       <c r="L10" s="4" t="n"/>
-      <c r="M10" s="13" t="n"/>
+      <c r="M10" s="10" t="n"/>
       <c r="N10" s="14" t="inlineStr">
         <is>
           <t>미실행</t>
@@ -1944,49 +2060,49 @@
           <t>P1</t>
         </is>
       </c>
-      <c r="C11" s="13" t="inlineStr">
+      <c r="C11" s="10" t="inlineStr">
         <is>
           <t>1 진입</t>
         </is>
       </c>
-      <c r="D11" s="13" t="inlineStr">
+      <c r="D11" s="10" t="inlineStr">
         <is>
           <t>네트워크 오류</t>
         </is>
       </c>
-      <c r="E11" s="13" t="inlineStr">
+      <c r="E11" s="10" t="inlineStr">
         <is>
           <t>①</t>
         </is>
       </c>
-      <c r="F11" s="13" t="inlineStr">
+      <c r="F11" s="10" t="inlineStr">
         <is>
           <t>앱</t>
         </is>
       </c>
-      <c r="G11" s="13" t="inlineStr">
+      <c r="G11" s="10" t="inlineStr">
         <is>
           <t>비행기 모드</t>
         </is>
       </c>
-      <c r="H11" s="13" t="inlineStr">
+      <c r="H11" s="10" t="inlineStr">
         <is>
           <t>홈 카드를 누른다</t>
         </is>
       </c>
-      <c r="I11" s="13" t="inlineStr">
+      <c r="I11" s="10" t="inlineStr">
         <is>
           <t>전체 화면 오류 + [다시 시도] · "참여자에게만" 문구가 나오지 않는다</t>
         </is>
       </c>
-      <c r="J11" s="13" t="inlineStr">
+      <c r="J11" s="10" t="inlineStr">
         <is>
           <t>P18</t>
         </is>
       </c>
-      <c r="K11" s="13" t="n"/>
+      <c r="K11" s="10" t="n"/>
       <c r="L11" s="4" t="n"/>
-      <c r="M11" s="13" t="n"/>
+      <c r="M11" s="10" t="n"/>
       <c r="N11" s="14" t="inlineStr">
         <is>
           <t>미실행</t>
@@ -2010,49 +2126,49 @@
           <t>P2</t>
         </is>
       </c>
-      <c r="C12" s="13" t="inlineStr">
+      <c r="C12" s="10" t="inlineStr">
         <is>
           <t>2 8개 섹션</t>
         </is>
       </c>
-      <c r="D12" s="13" t="inlineStr">
+      <c r="D12" s="10" t="inlineStr">
         <is>
           <t>01 표지</t>
         </is>
       </c>
-      <c r="E12" s="13" t="inlineStr">
+      <c r="E12" s="10" t="inlineStr">
         <is>
           <t>② ③ ④</t>
         </is>
       </c>
-      <c r="F12" s="13" t="inlineStr">
+      <c r="F12" s="10" t="inlineStr">
         <is>
           <t>앱 · 웹</t>
         </is>
       </c>
-      <c r="G12" s="13" t="inlineStr">
+      <c r="G12" s="10" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="H12" s="13" t="inlineStr">
+      <c r="H12" s="10" t="inlineStr">
         <is>
           <t>표지를 본다</t>
         </is>
       </c>
-      <c r="I12" s="13" t="inlineStr">
-        <is>
-          <t>배지 "2026 맬리브레인 3기" · "{마스킹 이름} 님," · "242일 중 N일의 기록이 담겨 있어요"</t>
-        </is>
-      </c>
-      <c r="J12" s="13" t="inlineStr">
-        <is>
-          <t>S1-01 · S1-02 · S1-03</t>
+      <c r="I12" s="10" t="inlineStr">
+        <is>
+          <t>피그마 목업처럼 배지 "2026 인천 남동구 보건소 치매 예방 3기" · "{마스킹 이름}님," · 기간 · 참여일 · 왼쪽 정렬 · 메달 그래픽</t>
+        </is>
+      </c>
+      <c r="J12" s="10" t="inlineStr">
+        <is>
+          <t>S1-01~04 · 목업 1097:791</t>
         </is>
       </c>
       <c r="K12" s="16" t="inlineStr">
         <is>
-          <t>cmp_01_cover.png</t>
+          <t>cmp_01.png</t>
         </is>
       </c>
       <c r="L12" s="17" t="inlineStr">
@@ -2062,7 +2178,7 @@
       </c>
       <c r="M12" s="18" t="inlineStr">
         <is>
-          <t>배지 문구 · 이름 띄어쓰기 다름 → BUG-03 · BUG-04</t>
+          <t>문구 일치 · 가운데 정렬 · 메달 없음 → BUG-03</t>
         </is>
       </c>
       <c r="N12" s="14" t="inlineStr">
@@ -2088,59 +2204,59 @@
           <t>P1</t>
         </is>
       </c>
-      <c r="C13" s="13" t="inlineStr">
+      <c r="C13" s="10" t="inlineStr">
         <is>
           <t>2 8개 섹션</t>
         </is>
       </c>
-      <c r="D13" s="13" t="inlineStr">
+      <c r="D13" s="10" t="inlineStr">
         <is>
           <t>02 숫자로 먼저</t>
         </is>
       </c>
-      <c r="E13" s="13" t="inlineStr">
+      <c r="E13" s="10" t="inlineStr">
         <is>
           <t>②</t>
         </is>
       </c>
-      <c r="F13" s="13" t="inlineStr">
+      <c r="F13" s="10" t="inlineStr">
         <is>
           <t>앱</t>
         </is>
       </c>
-      <c r="G13" s="13" t="inlineStr">
+      <c r="G13" s="10" t="inlineStr">
         <is>
           <t>§데이터 요청 5번 원값 수령</t>
         </is>
       </c>
-      <c r="H13" s="13" t="inlineStr">
+      <c r="H13" s="10" t="inlineStr">
         <is>
           <t>화면 숫자와 원값을 대조한다</t>
         </is>
       </c>
-      <c r="I13" s="13" t="inlineStr">
+      <c r="I13" s="10" t="inlineStr">
         <is>
           <t>뇌 점수 시작→종료 · 함께한 날 · 참여율 · 게임 횟수 · 마음 기록이 원값과 같다</t>
         </is>
       </c>
-      <c r="J13" s="13" t="inlineStr">
+      <c r="J13" s="10" t="inlineStr">
         <is>
           <t>S2 · F-01~F-04 · F-08</t>
         </is>
       </c>
       <c r="K13" s="16" t="inlineStr">
         <is>
-          <t>dev_02.png</t>
+          <t>cmp_02.png</t>
         </is>
       </c>
       <c r="L13" s="17" t="inlineStr">
         <is>
-          <t>통과</t>
+          <t>실패</t>
         </is>
       </c>
       <c r="M13" s="18" t="inlineStr">
         <is>
-          <t>샘플 69→77점 · 142일 · 59% · 862회 · 96일</t>
+          <t>숫자 정상 · 꺾은선이 거의 평평 → BUG-04</t>
         </is>
       </c>
       <c r="N13" s="14" t="inlineStr">
@@ -2166,57 +2282,61 @@
           <t>P2</t>
         </is>
       </c>
-      <c r="C14" s="13" t="inlineStr">
+      <c r="C14" s="10" t="inlineStr">
         <is>
           <t>2 8개 섹션</t>
         </is>
       </c>
-      <c r="D14" s="13" t="inlineStr">
+      <c r="D14" s="10" t="inlineStr">
         <is>
           <t>03 집중의 리듬</t>
         </is>
       </c>
-      <c r="E14" s="13" t="inlineStr">
+      <c r="E14" s="10" t="inlineStr">
         <is>
           <t>②</t>
         </is>
       </c>
-      <c r="F14" s="13" t="inlineStr">
+      <c r="F14" s="10" t="inlineStr">
         <is>
           <t>앱 · 웹</t>
         </is>
       </c>
-      <c r="G14" s="13" t="inlineStr">
+      <c r="G14" s="10" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="H14" s="13" t="inlineStr">
+      <c r="H14" s="10" t="inlineStr">
         <is>
           <t>요일 · 시간 · 막대를 본다</t>
         </is>
       </c>
-      <c r="I14" s="13" t="inlineStr">
+      <c r="I14" s="10" t="inlineStr">
         <is>
           <t>월~금만 · "프로그램 운영일은 평일(월–금)입니다"</t>
         </is>
       </c>
-      <c r="J14" s="13" t="inlineStr">
+      <c r="J14" s="10" t="inlineStr">
         <is>
           <t>S3 · F-07</t>
         </is>
       </c>
       <c r="K14" s="16" t="inlineStr">
         <is>
-          <t>dev_03.png</t>
+          <t>cmp_03.png</t>
         </is>
       </c>
       <c r="L14" s="17" t="inlineStr">
         <is>
-          <t>통과</t>
-        </is>
-      </c>
-      <c r="M14" s="18" t="n"/>
+          <t>실패</t>
+        </is>
+      </c>
+      <c r="M14" s="18" t="inlineStr">
+        <is>
+          <t>88% 강조색 · 멘트 카드 다름 → BUG-05</t>
+        </is>
+      </c>
       <c r="N14" s="14" t="inlineStr">
         <is>
           <t>미실행</t>
@@ -2240,49 +2360,49 @@
           <t>P2</t>
         </is>
       </c>
-      <c r="C15" s="13" t="inlineStr">
+      <c r="C15" s="10" t="inlineStr">
         <is>
           <t>2 8개 섹션</t>
         </is>
       </c>
-      <c r="D15" s="13" t="inlineStr">
+      <c r="D15" s="10" t="inlineStr">
         <is>
           <t>04 게임</t>
         </is>
       </c>
-      <c r="E15" s="13" t="inlineStr">
+      <c r="E15" s="10" t="inlineStr">
         <is>
           <t>②</t>
         </is>
       </c>
-      <c r="F15" s="13" t="inlineStr">
+      <c r="F15" s="10" t="inlineStr">
         <is>
           <t>앱 · 웹</t>
         </is>
       </c>
-      <c r="G15" s="13" t="inlineStr">
+      <c r="G15" s="10" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="H15" s="13" t="inlineStr">
+      <c r="H15" s="10" t="inlineStr">
         <is>
           <t>최다 게임 · 횟수 · 종수 · TOP3</t>
         </is>
       </c>
-      <c r="I15" s="13" t="inlineStr">
+      <c r="I15" s="10" t="inlineStr">
         <is>
           <t>"해본 게임 N종 / 전체 16종 중" · TOP3 정렬</t>
         </is>
       </c>
-      <c r="J15" s="13" t="inlineStr">
+      <c r="J15" s="10" t="inlineStr">
         <is>
           <t>S4 · F-03b · F-05</t>
         </is>
       </c>
       <c r="K15" s="16" t="inlineStr">
         <is>
-          <t>dev_04.png</t>
+          <t>cmp_04.png</t>
         </is>
       </c>
       <c r="L15" s="17" t="inlineStr">
@@ -2290,7 +2410,11 @@
           <t>통과</t>
         </is>
       </c>
-      <c r="M15" s="18" t="n"/>
+      <c r="M15" s="18" t="inlineStr">
+        <is>
+          <t>게임명 줄바꿈만 다름 → BUG-09 (P3)</t>
+        </is>
+      </c>
       <c r="N15" s="14" t="inlineStr">
         <is>
           <t>미실행</t>
@@ -2314,49 +2438,49 @@
           <t>P1</t>
         </is>
       </c>
-      <c r="C16" s="13" t="inlineStr">
+      <c r="C16" s="10" t="inlineStr">
         <is>
           <t>2 8개 섹션</t>
         </is>
       </c>
-      <c r="D16" s="13" t="inlineStr">
+      <c r="D16" s="10" t="inlineStr">
         <is>
           <t>04B 랭킹</t>
         </is>
       </c>
-      <c r="E16" s="13" t="inlineStr">
+      <c r="E16" s="10" t="inlineStr">
         <is>
           <t>② ①</t>
         </is>
       </c>
-      <c r="F16" s="13" t="inlineStr">
+      <c r="F16" s="10" t="inlineStr">
         <is>
           <t>앱 · 웹</t>
         </is>
       </c>
-      <c r="G16" s="13" t="inlineStr">
+      <c r="G16" s="10" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="H16" s="13" t="inlineStr">
+      <c r="H16" s="10" t="inlineStr">
         <is>
           <t>순위 · 상위 % 타일 · 배지 · 하단 문구</t>
         </is>
       </c>
-      <c r="I16" s="13" t="inlineStr">
+      <c r="I16" s="10" t="inlineStr">
         <is>
           <t>타일 % = 배지 % · 1~3위면 내 행 없음 · "아래로 {823-순위}명이 더 함께했어요" · 최하위면 문구 없음</t>
         </is>
       </c>
-      <c r="J16" s="13" t="inlineStr">
+      <c r="J16" s="10" t="inlineStr">
         <is>
           <t>S4B-04~08 · F-06 · F-06b · P08</t>
         </is>
       </c>
       <c r="K16" s="16" t="inlineStr">
         <is>
-          <t>dev_04B.png</t>
+          <t>cmp_04B.png</t>
         </is>
       </c>
       <c r="L16" s="17" t="inlineStr">
@@ -2366,7 +2490,7 @@
       </c>
       <c r="M16" s="18" t="inlineStr">
         <is>
-          <t>12위 · 상위 2% · 811명</t>
+          <t>12위 · 상위 2% · 811명 · 목업과 같음</t>
         </is>
       </c>
       <c r="N16" s="14" t="inlineStr">
@@ -2392,49 +2516,49 @@
           <t>P2</t>
         </is>
       </c>
-      <c r="C17" s="13" t="inlineStr">
+      <c r="C17" s="10" t="inlineStr">
         <is>
           <t>2 8개 섹션</t>
         </is>
       </c>
-      <c r="D17" s="13" t="inlineStr">
+      <c r="D17" s="10" t="inlineStr">
         <is>
           <t>05 마음</t>
         </is>
       </c>
-      <c r="E17" s="13" t="inlineStr">
+      <c r="E17" s="10" t="inlineStr">
         <is>
           <t>② + 측정 1회 · 0회 계정</t>
         </is>
       </c>
-      <c r="F17" s="13" t="inlineStr">
+      <c r="F17" s="10" t="inlineStr">
         <is>
           <t>앱 · 웹</t>
         </is>
       </c>
-      <c r="G17" s="13" t="inlineStr">
+      <c r="G17" s="10" t="inlineStr">
         <is>
           <t>측정 1회 · 0회 계정은 개발에 요청</t>
         </is>
       </c>
-      <c r="H17" s="13" t="inlineStr">
+      <c r="H17" s="10" t="inlineStr">
         <is>
           <t>게이지 · 상태 · 안내박스</t>
         </is>
       </c>
-      <c r="I17" s="13" t="inlineStr">
+      <c r="I17" s="10" t="inlineStr">
         <is>
           <t>종료 점수 구간으로 판정 · 1회면 고스트 없음 · 0회면 "검사 기록이 없습니다."</t>
         </is>
       </c>
-      <c r="J17" s="13" t="inlineStr">
+      <c r="J17" s="10" t="inlineStr">
         <is>
           <t>S5 · P03 · P04</t>
         </is>
       </c>
       <c r="K17" s="16" t="inlineStr">
         <is>
-          <t>dev_05.png</t>
+          <t>cmp_05.png</t>
         </is>
       </c>
       <c r="L17" s="17" t="inlineStr">
@@ -2444,7 +2568,7 @@
       </c>
       <c r="M17" s="18" t="inlineStr">
         <is>
-          <t>7→3점 양호</t>
+          <t>7→3점 양호 · 라벨 위치만 다름 → BUG-09 (P3)</t>
         </is>
       </c>
       <c r="N17" s="14" t="inlineStr">
@@ -2470,49 +2594,49 @@
           <t>P2</t>
         </is>
       </c>
-      <c r="C18" s="13" t="inlineStr">
+      <c r="C18" s="10" t="inlineStr">
         <is>
           <t>2 8개 섹션</t>
         </is>
       </c>
-      <c r="D18" s="13" t="inlineStr">
+      <c r="D18" s="10" t="inlineStr">
         <is>
           <t>06 걸음</t>
         </is>
       </c>
-      <c r="E18" s="13" t="inlineStr">
+      <c r="E18" s="10" t="inlineStr">
         <is>
           <t>② + 미연동 계정</t>
         </is>
       </c>
-      <c r="F18" s="13" t="inlineStr">
+      <c r="F18" s="10" t="inlineStr">
         <is>
           <t>앱 · 웹</t>
         </is>
       </c>
-      <c r="G18" s="13" t="inlineStr">
+      <c r="G18" s="10" t="inlineStr">
         <is>
           <t>미연동 계정은 개발에 요청</t>
         </is>
       </c>
-      <c r="H18" s="13" t="inlineStr">
+      <c r="H18" s="10" t="inlineStr">
         <is>
           <t>걸음 · 환산 · 칼로리</t>
         </is>
       </c>
-      <c r="I18" s="13" t="inlineStr">
+      <c r="I18" s="10" t="inlineStr">
         <is>
           <t>미연동이면 섹션 자체 없음 · 7km 미만이면 환산 카드 없음 · N=1이면 회차 없이 "걸었어요"</t>
         </is>
       </c>
-      <c r="J18" s="13" t="inlineStr">
+      <c r="J18" s="10" t="inlineStr">
         <is>
           <t>S6 · P16 · P17</t>
         </is>
       </c>
       <c r="K18" s="16" t="inlineStr">
         <is>
-          <t>dev_06.png</t>
+          <t>cmp_06.png</t>
         </is>
       </c>
       <c r="L18" s="17" t="inlineStr">
@@ -2522,7 +2646,7 @@
       </c>
       <c r="M18" s="18" t="inlineStr">
         <is>
-          <t>464km → 서울에서 부산까지 걸었어요</t>
+          <t>목업과 같음</t>
         </is>
       </c>
       <c r="N18" s="14" t="inlineStr">
@@ -2548,49 +2672,49 @@
           <t>P2</t>
         </is>
       </c>
-      <c r="C19" s="13" t="inlineStr">
+      <c r="C19" s="10" t="inlineStr">
         <is>
           <t>2 8개 섹션</t>
         </is>
       </c>
-      <c r="D19" s="13" t="inlineStr">
+      <c r="D19" s="10" t="inlineStr">
         <is>
           <t>스크롤 힌트</t>
         </is>
       </c>
-      <c r="E19" s="13" t="inlineStr">
+      <c r="E19" s="10" t="inlineStr">
         <is>
           <t>②</t>
         </is>
       </c>
-      <c r="F19" s="13" t="inlineStr">
+      <c r="F19" s="10" t="inlineStr">
         <is>
           <t>앱</t>
         </is>
       </c>
-      <c r="G19" s="13" t="inlineStr">
+      <c r="G19" s="10" t="inlineStr">
         <is>
           <t>작은 폰(iPhone SE급)</t>
         </is>
       </c>
-      <c r="H19" s="13" t="inlineStr">
+      <c r="H19" s="10" t="inlineStr">
         <is>
           <t>각 섹션에 들어간 직후와 스크롤한 뒤</t>
         </is>
       </c>
-      <c r="I19" s="13" t="inlineStr">
+      <c r="I19" s="10" t="inlineStr">
         <is>
           <t>진입 직후만 하단 고정 · 스크롤하면 풀림 · 본문을 계속 가리지 않음</t>
         </is>
       </c>
-      <c r="J19" s="13" t="inlineStr">
+      <c r="J19" s="10" t="inlineStr">
         <is>
           <t>S1-05 · FE-05</t>
         </is>
       </c>
       <c r="K19" s="16" t="inlineStr">
         <is>
-          <t>dev_04B.png</t>
+          <t>cmp_05.png</t>
         </is>
       </c>
       <c r="L19" s="17" t="inlineStr">
@@ -2600,7 +2724,7 @@
       </c>
       <c r="M19" s="18" t="inlineStr">
         <is>
-          <t>360×740 웹에서 진입 직후 힌트가 04B 하단 문구 위에 겹침 — 스크롤 후 풀리는지 앱에서 확인</t>
+          <t>375×812 웹에서 진입 직후 힌트가 05 안내박스를 가림 → BUG-08 · 앱에서 확인</t>
         </is>
       </c>
       <c r="N19" s="14" t="inlineStr">
@@ -2626,49 +2750,49 @@
           <t>P1</t>
         </is>
       </c>
-      <c r="C20" s="13" t="inlineStr">
+      <c r="C20" s="10" t="inlineStr">
         <is>
           <t>2 8개 섹션</t>
         </is>
       </c>
-      <c r="D20" s="13" t="inlineStr">
+      <c r="D20" s="10" t="inlineStr">
         <is>
           <t>닫기 버튼</t>
         </is>
       </c>
-      <c r="E20" s="13" t="inlineStr">
+      <c r="E20" s="10" t="inlineStr">
         <is>
           <t>①</t>
         </is>
       </c>
-      <c r="F20" s="13" t="inlineStr">
+      <c r="F20" s="10" t="inlineStr">
         <is>
           <t>앱</t>
         </is>
       </c>
-      <c r="G20" s="13" t="inlineStr">
+      <c r="G20" s="10" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="H20" s="13" t="inlineStr">
+      <c r="H20" s="10" t="inlineStr">
         <is>
           <t>아무 섹션에서 스크롤 중</t>
         </is>
       </c>
-      <c r="I20" s="13" t="inlineStr">
+      <c r="I20" s="10" t="inlineStr">
         <is>
           <t>✕가 항상 우상단에 고정</t>
         </is>
       </c>
-      <c r="J20" s="13" t="inlineStr">
+      <c r="J20" s="10" t="inlineStr">
         <is>
           <t>S1-06</t>
         </is>
       </c>
-      <c r="K20" s="13" t="n"/>
+      <c r="K20" s="10" t="n"/>
       <c r="L20" s="4" t="n"/>
-      <c r="M20" s="13" t="n"/>
+      <c r="M20" s="10" t="n"/>
       <c r="N20" s="14" t="inlineStr">
         <is>
           <t>미실행</t>
@@ -2692,49 +2816,49 @@
           <t>P3</t>
         </is>
       </c>
-      <c r="C21" s="13" t="inlineStr">
+      <c r="C21" s="10" t="inlineStr">
         <is>
           <t>2 8개 섹션</t>
         </is>
       </c>
-      <c r="D21" s="13" t="inlineStr">
+      <c r="D21" s="10" t="inlineStr">
         <is>
           <t>큰 글씨</t>
         </is>
       </c>
-      <c r="E21" s="13" t="inlineStr">
+      <c r="E21" s="10" t="inlineStr">
         <is>
           <t>②</t>
         </is>
       </c>
-      <c r="F21" s="13" t="inlineStr">
+      <c r="F21" s="10" t="inlineStr">
         <is>
           <t>앱</t>
         </is>
       </c>
-      <c r="G21" s="13" t="inlineStr">
+      <c r="G21" s="10" t="inlineStr">
         <is>
           <t>OS 글자 크기 최대</t>
         </is>
       </c>
-      <c r="H21" s="13" t="inlineStr">
+      <c r="H21" s="10" t="inlineStr">
         <is>
           <t>전 섹션을 본다</t>
         </is>
       </c>
-      <c r="I21" s="13" t="inlineStr">
+      <c r="I21" s="10" t="inlineStr">
         <is>
           <t>줄 넘침 · 겹침 · 잘림 없음</t>
         </is>
       </c>
-      <c r="J21" s="13" t="inlineStr">
+      <c r="J21" s="10" t="inlineStr">
         <is>
           <t>IA-R-14 · D-28</t>
         </is>
       </c>
-      <c r="K21" s="13" t="n"/>
+      <c r="K21" s="10" t="n"/>
       <c r="L21" s="4" t="n"/>
-      <c r="M21" s="13" t="n"/>
+      <c r="M21" s="10" t="n"/>
       <c r="N21" s="14" t="inlineStr">
         <is>
           <t>미실행</t>
@@ -2758,55 +2882,55 @@
           <t>P1</t>
         </is>
       </c>
-      <c r="C22" s="13" t="inlineStr">
+      <c r="C22" s="10" t="inlineStr">
         <is>
           <t>3 증서 저장</t>
         </is>
       </c>
-      <c r="D22" s="13" t="inlineStr">
+      <c r="D22" s="10" t="inlineStr">
         <is>
           <t>07 A</t>
         </is>
       </c>
-      <c r="E22" s="13" t="inlineStr">
+      <c r="E22" s="10" t="inlineStr">
         <is>
           <t>①</t>
         </is>
       </c>
-      <c r="F22" s="13" t="inlineStr">
+      <c r="F22" s="10" t="inlineStr">
         <is>
           <t>앱</t>
         </is>
       </c>
-      <c r="G22" s="13" t="inlineStr">
+      <c r="G22" s="10" t="inlineStr">
         <is>
           <t>사진 권한 허용</t>
         </is>
       </c>
-      <c r="H22" s="13" t="inlineStr">
+      <c r="H22" s="10" t="inlineStr">
         <is>
           <t>수료증 저장하기</t>
         </is>
       </c>
-      <c r="I22" s="13" t="inlineStr">
+      <c r="I22" s="10" t="inlineStr">
         <is>
           <t>사진첩에 1:1 이미지 1장 · 숫자 0이나 빈칸 없음</t>
         </is>
       </c>
-      <c r="J22" s="13" t="inlineStr">
+      <c r="J22" s="10" t="inlineStr">
         <is>
           <t>S7-10 · §12</t>
         </is>
       </c>
       <c r="K22" s="16" t="inlineStr">
         <is>
-          <t>dev_07_A.png</t>
+          <t>cmp_07A.png</t>
         </is>
       </c>
       <c r="L22" s="4" t="n"/>
-      <c r="M22" s="13" t="inlineStr">
-        <is>
-          <t>웹은 앱 브리지가 없어 저장 버튼 비활성(정상)</t>
+      <c r="M22" s="10" t="inlineStr">
+        <is>
+          <t>웹은 앱 브리지가 없어 저장 버튼 비활성(정상) · 테두리 장식 없음 → BUG-06</t>
         </is>
       </c>
       <c r="N22" s="14" t="inlineStr">
@@ -2832,49 +2956,49 @@
           <t>P1</t>
         </is>
       </c>
-      <c r="C23" s="13" t="inlineStr">
+      <c r="C23" s="10" t="inlineStr">
         <is>
           <t>3 증서 저장</t>
         </is>
       </c>
-      <c r="D23" s="13" t="inlineStr">
+      <c r="D23" s="10" t="inlineStr">
         <is>
           <t>07 A</t>
         </is>
       </c>
-      <c r="E23" s="13" t="inlineStr">
+      <c r="E23" s="10" t="inlineStr">
         <is>
           <t>①</t>
         </is>
       </c>
-      <c r="F23" s="13" t="inlineStr">
+      <c r="F23" s="10" t="inlineStr">
         <is>
           <t>앱</t>
         </is>
       </c>
-      <c r="G23" s="13" t="inlineStr">
+      <c r="G23" s="10" t="inlineStr">
         <is>
           <t>C-01 이후</t>
         </is>
       </c>
-      <c r="H23" s="13" t="inlineStr">
+      <c r="H23" s="10" t="inlineStr">
         <is>
           <t>파일명 · 형식 확인</t>
         </is>
       </c>
-      <c r="I23" s="13" t="inlineStr">
+      <c r="I23" s="10" t="inlineStr">
         <is>
           <t>맬리브레인_3기_수료증_{원문이름} · Android JPEG / iOS PNG</t>
         </is>
       </c>
-      <c r="J23" s="13" t="inlineStr">
+      <c r="J23" s="10" t="inlineStr">
         <is>
           <t>S7-10 · Q-10</t>
         </is>
       </c>
-      <c r="K23" s="13" t="n"/>
+      <c r="K23" s="10" t="n"/>
       <c r="L23" s="4" t="n"/>
-      <c r="M23" s="13" t="n"/>
+      <c r="M23" s="10" t="n"/>
       <c r="N23" s="14" t="inlineStr">
         <is>
           <t>미실행</t>
@@ -2898,49 +3022,49 @@
           <t>P2</t>
         </is>
       </c>
-      <c r="C24" s="13" t="inlineStr">
+      <c r="C24" s="10" t="inlineStr">
         <is>
           <t>3 증서 저장</t>
         </is>
       </c>
-      <c r="D24" s="13" t="inlineStr">
+      <c r="D24" s="10" t="inlineStr">
         <is>
           <t>07 B</t>
         </is>
       </c>
-      <c r="E24" s="13" t="inlineStr">
+      <c r="E24" s="10" t="inlineStr">
         <is>
           <t>③</t>
         </is>
       </c>
-      <c r="F24" s="13" t="inlineStr">
+      <c r="F24" s="10" t="inlineStr">
         <is>
           <t>앱 · 웹</t>
         </is>
       </c>
-      <c r="G24" s="13" t="inlineStr">
+      <c r="G24" s="10" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="H24" s="13" t="inlineStr">
+      <c r="H24" s="10" t="inlineStr">
         <is>
           <t>참여기록 저장하기</t>
         </is>
       </c>
-      <c r="I24" s="13" t="inlineStr">
+      <c r="I24" s="10" t="inlineStr">
         <is>
           <t>라벨 "참여기록 저장하기" · 파일명 …_참여기록_…</t>
         </is>
       </c>
-      <c r="J24" s="13" t="inlineStr">
+      <c r="J24" s="10" t="inlineStr">
         <is>
           <t>S7-10 · Q-02</t>
         </is>
       </c>
       <c r="K24" s="16" t="inlineStr">
         <is>
-          <t>dev_07_B.png</t>
+          <t>cmp_07B.png</t>
         </is>
       </c>
       <c r="L24" s="17" t="inlineStr">
@@ -2976,49 +3100,49 @@
           <t>P1</t>
         </is>
       </c>
-      <c r="C25" s="13" t="inlineStr">
+      <c r="C25" s="10" t="inlineStr">
         <is>
           <t>3 증서 저장</t>
         </is>
       </c>
-      <c r="D25" s="13" t="inlineStr">
+      <c r="D25" s="10" t="inlineStr">
         <is>
           <t>07 C</t>
         </is>
       </c>
-      <c r="E25" s="13" t="inlineStr">
+      <c r="E25" s="10" t="inlineStr">
         <is>
           <t>④</t>
         </is>
       </c>
-      <c r="F25" s="13" t="inlineStr">
+      <c r="F25" s="10" t="inlineStr">
         <is>
           <t>앱 · 웹</t>
         </is>
       </c>
-      <c r="G25" s="13" t="inlineStr">
+      <c r="G25" s="10" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="H25" s="13" t="inlineStr">
+      <c r="H25" s="10" t="inlineStr">
         <is>
           <t>증서 화면</t>
         </is>
       </c>
-      <c r="I25" s="13" t="inlineStr">
+      <c r="I25" s="10" t="inlineStr">
         <is>
           <t>저장 버튼 없음 · 참여 실적 줄 없음 · 4기 · 홈 버튼만</t>
         </is>
       </c>
-      <c r="J25" s="13" t="inlineStr">
+      <c r="J25" s="10" t="inlineStr">
         <is>
           <t>S7-08 · S7-10</t>
         </is>
       </c>
       <c r="K25" s="16" t="inlineStr">
         <is>
-          <t>dev_07_C.png</t>
+          <t>cmp_07C.png</t>
         </is>
       </c>
       <c r="L25" s="17" t="inlineStr">
@@ -3050,49 +3174,49 @@
           <t>P3</t>
         </is>
       </c>
-      <c r="C26" s="13" t="inlineStr">
+      <c r="C26" s="10" t="inlineStr">
         <is>
           <t>3 증서 저장</t>
         </is>
       </c>
-      <c r="D26" s="13" t="inlineStr">
+      <c r="D26" s="10" t="inlineStr">
         <is>
           <t>07 A</t>
         </is>
       </c>
-      <c r="E26" s="13" t="inlineStr">
+      <c r="E26" s="10" t="inlineStr">
         <is>
           <t>①</t>
         </is>
       </c>
-      <c r="F26" s="13" t="inlineStr">
+      <c r="F26" s="10" t="inlineStr">
         <is>
           <t>앱</t>
         </is>
       </c>
-      <c r="G26" s="13" t="inlineStr">
+      <c r="G26" s="10" t="inlineStr">
         <is>
           <t>사진 권한 거부</t>
         </is>
       </c>
-      <c r="H26" s="13" t="inlineStr">
+      <c r="H26" s="10" t="inlineStr">
         <is>
           <t>수료증 저장하기</t>
         </is>
       </c>
-      <c r="I26" s="13" t="inlineStr">
+      <c r="I26" s="10" t="inlineStr">
         <is>
           <t>권한 안내 · 앱이 멈추지 않음</t>
         </is>
       </c>
-      <c r="J26" s="13" t="inlineStr">
+      <c r="J26" s="10" t="inlineStr">
         <is>
           <t>P15</t>
         </is>
       </c>
-      <c r="K26" s="13" t="n"/>
+      <c r="K26" s="10" t="n"/>
       <c r="L26" s="4" t="n"/>
-      <c r="M26" s="13" t="n"/>
+      <c r="M26" s="10" t="n"/>
       <c r="N26" s="14" t="inlineStr">
         <is>
           <t>미실행</t>
@@ -3116,49 +3240,49 @@
           <t>P2</t>
         </is>
       </c>
-      <c r="C27" s="13" t="inlineStr">
+      <c r="C27" s="10" t="inlineStr">
         <is>
           <t>3 증서 저장</t>
         </is>
       </c>
-      <c r="D27" s="13" t="inlineStr">
+      <c r="D27" s="10" t="inlineStr">
         <is>
           <t>07 A</t>
         </is>
       </c>
-      <c r="E27" s="13" t="inlineStr">
+      <c r="E27" s="10" t="inlineStr">
         <is>
           <t>①</t>
         </is>
       </c>
-      <c r="F27" s="13" t="inlineStr">
+      <c r="F27" s="10" t="inlineStr">
         <is>
           <t>앱</t>
         </is>
       </c>
-      <c r="G27" s="13" t="inlineStr">
+      <c r="G27" s="10" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="H27" s="13" t="inlineStr">
+      <c r="H27" s="10" t="inlineStr">
         <is>
           <t>저장 후</t>
         </is>
       </c>
-      <c r="I27" s="13" t="inlineStr">
+      <c r="I27" s="10" t="inlineStr">
         <is>
           <t>리포트가 닫히지 않고 그대로</t>
         </is>
       </c>
-      <c r="J27" s="13" t="inlineStr">
+      <c r="J27" s="10" t="inlineStr">
         <is>
           <t>IA-R-10</t>
         </is>
       </c>
-      <c r="K27" s="13" t="n"/>
+      <c r="K27" s="10" t="n"/>
       <c r="L27" s="4" t="n"/>
-      <c r="M27" s="13" t="n"/>
+      <c r="M27" s="10" t="n"/>
       <c r="N27" s="14" t="inlineStr">
         <is>
           <t>미실행</t>
@@ -3182,49 +3306,49 @@
           <t>P2</t>
         </is>
       </c>
-      <c r="C28" s="13" t="inlineStr">
+      <c r="C28" s="10" t="inlineStr">
         <is>
           <t>3 증서 저장</t>
         </is>
       </c>
-      <c r="D28" s="13" t="inlineStr">
+      <c r="D28" s="10" t="inlineStr">
         <is>
           <t>07 A</t>
         </is>
       </c>
-      <c r="E28" s="13" t="inlineStr">
+      <c r="E28" s="10" t="inlineStr">
         <is>
           <t>①</t>
         </is>
       </c>
-      <c r="F28" s="13" t="inlineStr">
+      <c r="F28" s="10" t="inlineStr">
         <is>
           <t>앱 · 웹</t>
         </is>
       </c>
-      <c r="G28" s="13" t="inlineStr">
+      <c r="G28" s="10" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="H28" s="13" t="inlineStr">
+      <c r="H28" s="10" t="inlineStr">
         <is>
           <t>증서 이름 확인</t>
         </is>
       </c>
-      <c r="I28" s="13" t="inlineStr">
+      <c r="I28" s="10" t="inlineStr">
         <is>
           <t>표지는 마스킹(김*리) · 증서는 원문 이름</t>
         </is>
       </c>
-      <c r="J28" s="13" t="inlineStr">
+      <c r="J28" s="10" t="inlineStr">
         <is>
           <t>S7-06 · P12</t>
         </is>
       </c>
       <c r="K28" s="16" t="inlineStr">
         <is>
-          <t>dev_07_A.png</t>
+          <t>cmp_07A.png</t>
         </is>
       </c>
       <c r="L28" s="17" t="inlineStr">
@@ -3256,59 +3380,59 @@
           <t>P1</t>
         </is>
       </c>
-      <c r="C29" s="13" t="inlineStr">
+      <c r="C29" s="10" t="inlineStr">
         <is>
           <t>4 4기 신청</t>
         </is>
       </c>
-      <c r="D29" s="13" t="inlineStr">
+      <c r="D29" s="10" t="inlineStr">
         <is>
           <t>07-h 시트</t>
         </is>
       </c>
-      <c r="E29" s="13" t="inlineStr">
+      <c r="E29" s="10" t="inlineStr">
         <is>
           <t>①</t>
         </is>
       </c>
-      <c r="F29" s="13" t="inlineStr">
+      <c r="F29" s="10" t="inlineStr">
         <is>
           <t>앱 · 웹</t>
         </is>
       </c>
-      <c r="G29" s="13" t="inlineStr">
+      <c r="G29" s="10" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="H29" s="13" t="inlineStr">
+      <c r="H29" s="10" t="inlineStr">
         <is>
           <t>4기도 참여하기</t>
         </is>
       </c>
-      <c r="I29" s="13" t="inlineStr">
+      <c r="I29" s="10" t="inlineStr">
         <is>
           <t>바텀시트 · 문구는 결정 Q-1대로 · [닫기] [네, 신청합니다]</t>
         </is>
       </c>
-      <c r="J29" s="13" t="inlineStr">
+      <c r="J29" s="10" t="inlineStr">
         <is>
           <t>07-h · K-13</t>
         </is>
       </c>
       <c r="K29" s="16" t="inlineStr">
         <is>
-          <t>dev_07h_sheet.png</t>
+          <t>cmp_07h.png</t>
         </is>
       </c>
       <c r="L29" s="17" t="inlineStr">
         <is>
-          <t>보류</t>
+          <t>통과</t>
         </is>
       </c>
       <c r="M29" s="18" t="inlineStr">
         <is>
-          <t>시트에 "4기" 없음 → 결정 Q-1</t>
+          <t>목업과 같음 · 명칭에 4기 없음은 결정 Q-1</t>
         </is>
       </c>
       <c r="N29" s="14" t="inlineStr">
@@ -3334,47 +3458,47 @@
           <t>P2</t>
         </is>
       </c>
-      <c r="C30" s="13" t="inlineStr">
+      <c r="C30" s="10" t="inlineStr">
         <is>
           <t>4 4기 신청</t>
         </is>
       </c>
-      <c r="D30" s="13" t="inlineStr">
+      <c r="D30" s="10" t="inlineStr">
         <is>
           <t>07-h 시트</t>
         </is>
       </c>
-      <c r="E30" s="13" t="inlineStr">
+      <c r="E30" s="10" t="inlineStr">
         <is>
           <t>①</t>
         </is>
       </c>
-      <c r="F30" s="13" t="inlineStr">
+      <c r="F30" s="10" t="inlineStr">
         <is>
           <t>앱 · 웹</t>
         </is>
       </c>
-      <c r="G30" s="13" t="inlineStr">
+      <c r="G30" s="10" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="H30" s="13" t="inlineStr">
+      <c r="H30" s="10" t="inlineStr">
         <is>
           <t>[닫기] / 딤 탭</t>
         </is>
       </c>
-      <c r="I30" s="13" t="inlineStr">
+      <c r="I30" s="10" t="inlineStr">
         <is>
           <t>시트만 닫힘 · 신청 저장 안 됨</t>
         </is>
       </c>
-      <c r="J30" s="13" t="inlineStr">
+      <c r="J30" s="10" t="inlineStr">
         <is>
           <t>07-h</t>
         </is>
       </c>
-      <c r="K30" s="13" t="n"/>
+      <c r="K30" s="10" t="n"/>
       <c r="L30" s="17" t="inlineStr">
         <is>
           <t>통과</t>
@@ -3408,49 +3532,49 @@
           <t>P1</t>
         </is>
       </c>
-      <c r="C31" s="13" t="inlineStr">
+      <c r="C31" s="10" t="inlineStr">
         <is>
           <t>4 4기 신청</t>
         </is>
       </c>
-      <c r="D31" s="13" t="inlineStr">
+      <c r="D31" s="10" t="inlineStr">
         <is>
           <t>08 완료</t>
         </is>
       </c>
-      <c r="E31" s="13" t="inlineStr">
+      <c r="E31" s="10" t="inlineStr">
         <is>
           <t>①</t>
         </is>
       </c>
-      <c r="F31" s="13" t="inlineStr">
+      <c r="F31" s="10" t="inlineStr">
         <is>
           <t>앱 · 웹</t>
         </is>
       </c>
-      <c r="G31" s="13" t="inlineStr">
+      <c r="G31" s="10" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="H31" s="13" t="inlineStr">
+      <c r="H31" s="10" t="inlineStr">
         <is>
           <t>[네, 신청합니다]</t>
         </is>
       </c>
-      <c r="I31" s="13" t="inlineStr">
+      <c r="I31" s="10" t="inlineStr">
         <is>
           <t>완료 화면 · 본문 4줄 "4기가 시작될 때 보건소에서 연락드리겠습니다. 자세한 문의사항은 032-453-6160으로 문의 바랍니다. 감사합니다."</t>
         </is>
       </c>
-      <c r="J31" s="13" t="inlineStr">
+      <c r="J31" s="10" t="inlineStr">
         <is>
           <t>SC-RP-08 · S8-05 · K-14</t>
         </is>
       </c>
       <c r="K31" s="16" t="inlineStr">
         <is>
-          <t>cmp_08_done.png</t>
+          <t>cmp_08.png</t>
         </is>
       </c>
       <c r="L31" s="17" t="inlineStr">
@@ -3460,7 +3584,7 @@
       </c>
       <c r="M31" s="18" t="inlineStr">
         <is>
-          <t>첫 줄 누락 · 번호 6163 · 배치 다름 → BUG-01 · 02 · 05</t>
+          <t>배치는 목업과 같음 · 첫 줄 누락 · 번호 6163 → BUG-01 · 02</t>
         </is>
       </c>
       <c r="N31" s="14" t="inlineStr">
@@ -3486,49 +3610,49 @@
           <t>P2</t>
         </is>
       </c>
-      <c r="C32" s="13" t="inlineStr">
+      <c r="C32" s="10" t="inlineStr">
         <is>
           <t>4 4기 신청</t>
         </is>
       </c>
-      <c r="D32" s="13" t="inlineStr">
+      <c r="D32" s="10" t="inlineStr">
         <is>
           <t>08 완료</t>
         </is>
       </c>
-      <c r="E32" s="13" t="inlineStr">
+      <c r="E32" s="10" t="inlineStr">
         <is>
           <t>①</t>
         </is>
       </c>
-      <c r="F32" s="13" t="inlineStr">
+      <c r="F32" s="10" t="inlineStr">
         <is>
           <t>앱</t>
         </is>
       </c>
-      <c r="G32" s="13" t="inlineStr">
+      <c r="G32" s="10" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="H32" s="13" t="inlineStr">
+      <c r="H32" s="10" t="inlineStr">
         <is>
           <t>[네, 신청합니다] 연타</t>
         </is>
       </c>
-      <c r="I32" s="13" t="inlineStr">
+      <c r="I32" s="10" t="inlineStr">
         <is>
           <t>신청 1건만 저장</t>
         </is>
       </c>
-      <c r="J32" s="13" t="inlineStr">
+      <c r="J32" s="10" t="inlineStr">
         <is>
           <t>IA-R-12</t>
         </is>
       </c>
-      <c r="K32" s="13" t="n"/>
+      <c r="K32" s="10" t="n"/>
       <c r="L32" s="4" t="n"/>
-      <c r="M32" s="13" t="n"/>
+      <c r="M32" s="10" t="n"/>
       <c r="N32" s="14" t="inlineStr">
         <is>
           <t>미실행</t>
@@ -3552,49 +3676,49 @@
           <t>P1</t>
         </is>
       </c>
-      <c r="C33" s="13" t="inlineStr">
+      <c r="C33" s="10" t="inlineStr">
         <is>
           <t>4 4기 신청</t>
         </is>
       </c>
-      <c r="D33" s="13" t="inlineStr">
+      <c r="D33" s="10" t="inlineStr">
         <is>
           <t>07-l</t>
         </is>
       </c>
-      <c r="E33" s="13" t="inlineStr">
+      <c r="E33" s="10" t="inlineStr">
         <is>
           <t>①</t>
         </is>
       </c>
-      <c r="F33" s="13" t="inlineStr">
+      <c r="F33" s="10" t="inlineStr">
         <is>
           <t>앱 · 웹</t>
         </is>
       </c>
-      <c r="G33" s="13" t="inlineStr">
+      <c r="G33" s="10" t="inlineStr">
         <is>
           <t>A-03 이후</t>
         </is>
       </c>
-      <c r="H33" s="13" t="inlineStr">
+      <c r="H33" s="10" t="inlineStr">
         <is>
           <t>홈 → 리포트 다시 열기</t>
         </is>
       </c>
-      <c r="I33" s="13" t="inlineStr">
+      <c r="I33" s="10" t="inlineStr">
         <is>
           <t>4기 버튼 비활성 + "4기 신청이 완료되었습니다"</t>
         </is>
       </c>
-      <c r="J33" s="13" t="inlineStr">
+      <c r="J33" s="10" t="inlineStr">
         <is>
           <t>07-l · IA-R-12</t>
         </is>
       </c>
       <c r="K33" s="16" t="inlineStr">
         <is>
-          <t>dev_07_l.png</t>
+          <t>cmp_07l.png</t>
         </is>
       </c>
       <c r="L33" s="17" t="inlineStr">
@@ -3604,7 +3728,7 @@
       </c>
       <c r="M33" s="18" t="inlineStr">
         <is>
-          <t>state=07l</t>
+          <t>state=07l · 목업과 같음</t>
         </is>
       </c>
       <c r="N33" s="14" t="inlineStr">
@@ -3630,49 +3754,49 @@
           <t>P1</t>
         </is>
       </c>
-      <c r="C34" s="13" t="inlineStr">
+      <c r="C34" s="10" t="inlineStr">
         <is>
           <t>4 4기 신청</t>
         </is>
       </c>
-      <c r="D34" s="13" t="inlineStr">
+      <c r="D34" s="10" t="inlineStr">
         <is>
           <t>07-l</t>
         </is>
       </c>
-      <c r="E34" s="13" t="inlineStr">
+      <c r="E34" s="10" t="inlineStr">
         <is>
           <t>①</t>
         </is>
       </c>
-      <c r="F34" s="13" t="inlineStr">
+      <c r="F34" s="10" t="inlineStr">
         <is>
           <t>앱</t>
         </is>
       </c>
-      <c r="G34" s="13" t="inlineStr">
+      <c r="G34" s="10" t="inlineStr">
         <is>
           <t>A-03 이후</t>
         </is>
       </c>
-      <c r="H34" s="13" t="inlineStr">
+      <c r="H34" s="10" t="inlineStr">
         <is>
           <t>다른 폰에서 같은 계정 로그인</t>
         </is>
       </c>
-      <c r="I34" s="13" t="inlineStr">
+      <c r="I34" s="10" t="inlineStr">
         <is>
           <t>07-l 상태 그대로 (서버 값 기준)</t>
         </is>
       </c>
-      <c r="J34" s="13" t="inlineStr">
+      <c r="J34" s="10" t="inlineStr">
         <is>
           <t>apply.season4_applied</t>
         </is>
       </c>
-      <c r="K34" s="13" t="n"/>
+      <c r="K34" s="10" t="n"/>
       <c r="L34" s="4" t="n"/>
-      <c r="M34" s="13" t="n"/>
+      <c r="M34" s="10" t="n"/>
       <c r="N34" s="14" t="inlineStr">
         <is>
           <t>미실행</t>
@@ -3696,47 +3820,47 @@
           <t>P1</t>
         </is>
       </c>
-      <c r="C35" s="13" t="inlineStr">
+      <c r="C35" s="10" t="inlineStr">
         <is>
           <t>4 4기 신청</t>
         </is>
       </c>
-      <c r="D35" s="13" t="inlineStr">
+      <c r="D35" s="10" t="inlineStr">
         <is>
           <t>08-a 실패</t>
         </is>
       </c>
-      <c r="E35" s="13" t="inlineStr">
+      <c r="E35" s="10" t="inlineStr">
         <is>
           <t>①</t>
         </is>
       </c>
-      <c r="F35" s="13" t="inlineStr">
+      <c r="F35" s="10" t="inlineStr">
         <is>
           <t>앱</t>
         </is>
       </c>
-      <c r="G35" s="13" t="inlineStr">
+      <c r="G35" s="10" t="inlineStr">
         <is>
           <t>비행기 모드</t>
         </is>
       </c>
-      <c r="H35" s="13" t="inlineStr">
+      <c r="H35" s="10" t="inlineStr">
         <is>
           <t>[네, 신청합니다]</t>
         </is>
       </c>
-      <c r="I35" s="13" t="inlineStr">
-        <is>
-          <t>실패 화면 · "신청하지 못했습니다." · 032-453-6160 · [다시 시도] 동작</t>
-        </is>
-      </c>
-      <c r="J35" s="13" t="inlineStr">
+      <c r="I35" s="10" t="inlineStr">
+        <is>
+          <t>실패 화면 · 제목은 FIG-03 결정대로 · 032-453-6160 · [다시 시도] 누르면 확인 없이 자동 재신청</t>
+        </is>
+      </c>
+      <c r="J35" s="10" t="inlineStr">
         <is>
           <t>08-a · S8-06</t>
         </is>
       </c>
-      <c r="K35" s="13" t="n"/>
+      <c r="K35" s="10" t="n"/>
       <c r="L35" s="17" t="inlineStr">
         <is>
           <t>미실행</t>
@@ -3770,49 +3894,49 @@
           <t>P2</t>
         </is>
       </c>
-      <c r="C36" s="13" t="inlineStr">
+      <c r="C36" s="10" t="inlineStr">
         <is>
           <t>4 4기 신청</t>
         </is>
       </c>
-      <c r="D36" s="13" t="inlineStr">
+      <c r="D36" s="10" t="inlineStr">
         <is>
           <t>07-l</t>
         </is>
       </c>
-      <c r="E36" s="13" t="inlineStr">
+      <c r="E36" s="10" t="inlineStr">
         <is>
           <t>②</t>
         </is>
       </c>
-      <c r="F36" s="13" t="inlineStr">
+      <c r="F36" s="10" t="inlineStr">
         <is>
           <t>앱</t>
         </is>
       </c>
-      <c r="G36" s="13" t="inlineStr">
+      <c r="G36" s="10" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="H36" s="13" t="inlineStr">
+      <c r="H36" s="10" t="inlineStr">
         <is>
           <t>리포트 열기</t>
         </is>
       </c>
-      <c r="I36" s="13" t="inlineStr">
+      <c r="I36" s="10" t="inlineStr">
         <is>
           <t>처음부터 07-l</t>
         </is>
       </c>
-      <c r="J36" s="13" t="inlineStr">
+      <c r="J36" s="10" t="inlineStr">
         <is>
           <t>07-l</t>
         </is>
       </c>
-      <c r="K36" s="13" t="n"/>
+      <c r="K36" s="10" t="n"/>
       <c r="L36" s="4" t="n"/>
-      <c r="M36" s="13" t="n"/>
+      <c r="M36" s="10" t="n"/>
       <c r="N36" s="14" t="inlineStr">
         <is>
           <t>미실행</t>
@@ -3836,49 +3960,49 @@
           <t>P1</t>
         </is>
       </c>
-      <c r="C37" s="13" t="inlineStr">
+      <c r="C37" s="10" t="inlineStr">
         <is>
           <t>4 4기 신청</t>
         </is>
       </c>
-      <c r="D37" s="13" t="inlineStr">
+      <c r="D37" s="10" t="inlineStr">
         <is>
           <t>07-m</t>
         </is>
       </c>
-      <c r="E37" s="13" t="inlineStr">
+      <c r="E37" s="10" t="inlineStr">
         <is>
           <t>⑤</t>
         </is>
       </c>
-      <c r="F37" s="13" t="inlineStr">
+      <c r="F37" s="10" t="inlineStr">
         <is>
           <t>앱</t>
         </is>
       </c>
-      <c r="G37" s="13" t="inlineStr">
+      <c r="G37" s="10" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="H37" s="13" t="inlineStr">
+      <c r="H37" s="10" t="inlineStr">
         <is>
           <t>증서 화면</t>
         </is>
       </c>
-      <c r="I37" s="13" t="inlineStr">
+      <c r="I37" s="10" t="inlineStr">
         <is>
           <t>4기 버튼 없음</t>
         </is>
       </c>
-      <c r="J37" s="13" t="inlineStr">
+      <c r="J37" s="10" t="inlineStr">
         <is>
           <t>07-m</t>
         </is>
       </c>
-      <c r="K37" s="13" t="n"/>
+      <c r="K37" s="10" t="n"/>
       <c r="L37" s="4" t="n"/>
-      <c r="M37" s="13" t="n"/>
+      <c r="M37" s="10" t="n"/>
       <c r="N37" s="14" t="inlineStr">
         <is>
           <t>미실행</t>
@@ -3902,49 +4026,49 @@
           <t>P2</t>
         </is>
       </c>
-      <c r="C38" s="13" t="inlineStr">
+      <c r="C38" s="10" t="inlineStr">
         <is>
           <t>4 4기 신청</t>
         </is>
       </c>
-      <c r="D38" s="13" t="inlineStr">
+      <c r="D38" s="10" t="inlineStr">
         <is>
           <t>노출 시점</t>
         </is>
       </c>
-      <c r="E38" s="13" t="inlineStr">
+      <c r="E38" s="10" t="inlineStr">
         <is>
           <t>운영</t>
         </is>
       </c>
-      <c r="F38" s="13" t="inlineStr">
+      <c r="F38" s="10" t="inlineStr">
         <is>
           <t>앱</t>
         </is>
       </c>
-      <c r="G38" s="13" t="inlineStr">
+      <c r="G38" s="10" t="inlineStr">
         <is>
           <t>10/27 출시 빌드</t>
         </is>
       </c>
-      <c r="H38" s="13" t="inlineStr">
+      <c r="H38" s="10" t="inlineStr">
         <is>
           <t>출시 전 · 후 버튼 노출</t>
         </is>
       </c>
-      <c r="I38" s="13" t="inlineStr">
+      <c r="I38" s="10" t="inlineStr">
         <is>
           <t>10/27부터 노출</t>
         </is>
       </c>
-      <c r="J38" s="13" t="inlineStr">
+      <c r="J38" s="10" t="inlineStr">
         <is>
           <t>S7-11</t>
         </is>
       </c>
-      <c r="K38" s="13" t="n"/>
+      <c r="K38" s="10" t="n"/>
       <c r="L38" s="4" t="n"/>
-      <c r="M38" s="13" t="n"/>
+      <c r="M38" s="10" t="n"/>
       <c r="N38" s="14" t="inlineStr">
         <is>
           <t>미실행</t>
@@ -3968,49 +4092,49 @@
           <t>P1</t>
         </is>
       </c>
-      <c r="C39" s="13" t="inlineStr">
+      <c r="C39" s="10" t="inlineStr">
         <is>
           <t>5 닫기 · 뒤로가기</t>
         </is>
       </c>
-      <c r="D39" s="13" t="inlineStr">
+      <c r="D39" s="10" t="inlineStr">
         <is>
           <t>공통</t>
         </is>
       </c>
-      <c r="E39" s="13" t="inlineStr">
+      <c r="E39" s="10" t="inlineStr">
         <is>
           <t>①</t>
         </is>
       </c>
-      <c r="F39" s="13" t="inlineStr">
+      <c r="F39" s="10" t="inlineStr">
         <is>
           <t>앱</t>
         </is>
       </c>
-      <c r="G39" s="13" t="inlineStr">
+      <c r="G39" s="10" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="H39" s="13" t="inlineStr">
+      <c r="H39" s="10" t="inlineStr">
         <is>
           <t>아무 섹션에서 ✕</t>
         </is>
       </c>
-      <c r="I39" s="13" t="inlineStr">
+      <c r="I39" s="10" t="inlineStr">
         <is>
           <t>홈으로 복귀</t>
         </is>
       </c>
-      <c r="J39" s="13" t="inlineStr">
+      <c r="J39" s="10" t="inlineStr">
         <is>
           <t>IA-R-05</t>
         </is>
       </c>
-      <c r="K39" s="13" t="n"/>
+      <c r="K39" s="10" t="n"/>
       <c r="L39" s="4" t="n"/>
-      <c r="M39" s="13" t="n"/>
+      <c r="M39" s="10" t="n"/>
       <c r="N39" s="14" t="inlineStr">
         <is>
           <t>미실행</t>
@@ -4034,49 +4158,49 @@
           <t>P1</t>
         </is>
       </c>
-      <c r="C40" s="13" t="inlineStr">
+      <c r="C40" s="10" t="inlineStr">
         <is>
           <t>5 닫기 · 뒤로가기</t>
         </is>
       </c>
-      <c r="D40" s="13" t="inlineStr">
+      <c r="D40" s="10" t="inlineStr">
         <is>
           <t>공통</t>
         </is>
       </c>
-      <c r="E40" s="13" t="inlineStr">
+      <c r="E40" s="10" t="inlineStr">
         <is>
           <t>①</t>
         </is>
       </c>
-      <c r="F40" s="13" t="inlineStr">
+      <c r="F40" s="10" t="inlineStr">
         <is>
           <t>Android</t>
         </is>
       </c>
-      <c r="G40" s="13" t="inlineStr">
+      <c r="G40" s="10" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="H40" s="13" t="inlineStr">
+      <c r="H40" s="10" t="inlineStr">
         <is>
           <t>리포트 / 시트 열림 / 완료 화면에서 뒤로가기</t>
         </is>
       </c>
-      <c r="I40" s="13" t="inlineStr">
+      <c r="I40" s="10" t="inlineStr">
         <is>
           <t>시트가 열려 있으면 시트만 닫힘 · 그 외 홈</t>
         </is>
       </c>
-      <c r="J40" s="13" t="inlineStr">
+      <c r="J40" s="10" t="inlineStr">
         <is>
           <t>IA-R-05</t>
         </is>
       </c>
-      <c r="K40" s="13" t="n"/>
+      <c r="K40" s="10" t="n"/>
       <c r="L40" s="4" t="n"/>
-      <c r="M40" s="13" t="n"/>
+      <c r="M40" s="10" t="n"/>
       <c r="N40" s="14" t="inlineStr">
         <is>
           <t>미실행</t>
@@ -4100,49 +4224,49 @@
           <t>P2</t>
         </is>
       </c>
-      <c r="C41" s="13" t="inlineStr">
+      <c r="C41" s="10" t="inlineStr">
         <is>
           <t>5 닫기 · 뒤로가기</t>
         </is>
       </c>
-      <c r="D41" s="13" t="inlineStr">
+      <c r="D41" s="10" t="inlineStr">
         <is>
           <t>공통</t>
         </is>
       </c>
-      <c r="E41" s="13" t="inlineStr">
+      <c r="E41" s="10" t="inlineStr">
         <is>
           <t>①</t>
         </is>
       </c>
-      <c r="F41" s="13" t="inlineStr">
+      <c r="F41" s="10" t="inlineStr">
         <is>
           <t>iOS</t>
         </is>
       </c>
-      <c r="G41" s="13" t="inlineStr">
+      <c r="G41" s="10" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="H41" s="13" t="inlineStr">
+      <c r="H41" s="10" t="inlineStr">
         <is>
           <t>밀어서 닫기</t>
         </is>
       </c>
-      <c r="I41" s="13" t="inlineStr">
+      <c r="I41" s="10" t="inlineStr">
         <is>
           <t>홈 복귀 · 화면 깨짐 없음</t>
         </is>
       </c>
-      <c r="J41" s="13" t="inlineStr">
+      <c r="J41" s="10" t="inlineStr">
         <is>
           <t>개발 B-7</t>
         </is>
       </c>
-      <c r="K41" s="13" t="n"/>
+      <c r="K41" s="10" t="n"/>
       <c r="L41" s="4" t="n"/>
-      <c r="M41" s="13" t="n"/>
+      <c r="M41" s="10" t="n"/>
       <c r="N41" s="14" t="inlineStr">
         <is>
           <t>미실행</t>
@@ -4166,49 +4290,49 @@
           <t>P2</t>
         </is>
       </c>
-      <c r="C42" s="13" t="inlineStr">
+      <c r="C42" s="10" t="inlineStr">
         <is>
           <t>5 닫기 · 뒤로가기</t>
         </is>
       </c>
-      <c r="D42" s="13" t="inlineStr">
+      <c r="D42" s="10" t="inlineStr">
         <is>
           <t>08 완료</t>
         </is>
       </c>
-      <c r="E42" s="13" t="inlineStr">
+      <c r="E42" s="10" t="inlineStr">
         <is>
           <t>①</t>
         </is>
       </c>
-      <c r="F42" s="13" t="inlineStr">
+      <c r="F42" s="10" t="inlineStr">
         <is>
           <t>앱</t>
         </is>
       </c>
-      <c r="G42" s="13" t="inlineStr">
+      <c r="G42" s="10" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="H42" s="13" t="inlineStr">
+      <c r="H42" s="10" t="inlineStr">
         <is>
           <t>[홈으로 돌아가기]</t>
         </is>
       </c>
-      <c r="I42" s="13" t="inlineStr">
+      <c r="I42" s="10" t="inlineStr">
         <is>
           <t>홈 복귀</t>
         </is>
       </c>
-      <c r="J42" s="13" t="inlineStr">
+      <c r="J42" s="10" t="inlineStr">
         <is>
           <t>S8-07</t>
         </is>
       </c>
-      <c r="K42" s="13" t="n"/>
+      <c r="K42" s="10" t="n"/>
       <c r="L42" s="4" t="n"/>
-      <c r="M42" s="13" t="inlineStr">
+      <c r="M42" s="10" t="inlineStr">
         <is>
           <t>웹에서는 동작 안 하는 게 정상</t>
         </is>
@@ -4236,49 +4360,49 @@
           <t>P2</t>
         </is>
       </c>
-      <c r="C43" s="13" t="inlineStr">
+      <c r="C43" s="10" t="inlineStr">
         <is>
           <t>6 4기 전환</t>
         </is>
       </c>
-      <c r="D43" s="13" t="inlineStr">
+      <c r="D43" s="10" t="inlineStr">
         <is>
           <t>체험 홈</t>
         </is>
       </c>
-      <c r="E43" s="13" t="inlineStr">
+      <c r="E43" s="10" t="inlineStr">
         <is>
           <t>4기 승인 계정</t>
         </is>
       </c>
-      <c r="F43" s="13" t="inlineStr">
+      <c r="F43" s="10" t="inlineStr">
         <is>
           <t>앱</t>
         </is>
       </c>
-      <c r="G43" s="13" t="inlineStr">
+      <c r="G43" s="10" t="inlineStr">
         <is>
           <t>개발에 4기 시작일 당겨 달라고 요청</t>
         </is>
       </c>
-      <c r="H43" s="13" t="inlineStr">
+      <c r="H43" s="10" t="inlineStr">
         <is>
           <t>4기 홈 전환 후 확인</t>
         </is>
       </c>
-      <c r="I43" s="13" t="inlineStr">
+      <c r="I43" s="10" t="inlineStr">
         <is>
           <t>리포트 카드 사라짐 · 진행 내역으로는 열림</t>
         </is>
       </c>
-      <c r="J43" s="13" t="inlineStr">
+      <c r="J43" s="10" t="inlineStr">
         <is>
           <t>IA-R-08 · F4</t>
         </is>
       </c>
-      <c r="K43" s="13" t="n"/>
+      <c r="K43" s="10" t="n"/>
       <c r="L43" s="4" t="n"/>
-      <c r="M43" s="13" t="n"/>
+      <c r="M43" s="10" t="n"/>
       <c r="N43" s="14" t="inlineStr">
         <is>
           <t>미실행</t>
@@ -4302,47 +4426,47 @@
           <t>P2</t>
         </is>
       </c>
-      <c r="C44" s="13" t="inlineStr">
+      <c r="C44" s="10" t="inlineStr">
         <is>
           <t>6 측정</t>
         </is>
       </c>
-      <c r="D44" s="13" t="inlineStr">
+      <c r="D44" s="10" t="inlineStr">
         <is>
           <t>이벤트</t>
         </is>
       </c>
-      <c r="E44" s="13" t="inlineStr">
+      <c r="E44" s="10" t="inlineStr">
         <is>
           <t>①</t>
         </is>
       </c>
-      <c r="F44" s="13" t="inlineStr">
+      <c r="F44" s="10" t="inlineStr">
         <is>
           <t>앱</t>
         </is>
       </c>
-      <c r="G44" s="13" t="inlineStr">
+      <c r="G44" s="10" t="inlineStr">
         <is>
           <t>개발에 이벤트 로그 확인 요청</t>
         </is>
       </c>
-      <c r="H44" s="13" t="inlineStr">
+      <c r="H44" s="10" t="inlineStr">
         <is>
           <t>카드 / 자동 팝업 / 진행 내역으로 각각 진입</t>
         </is>
       </c>
-      <c r="I44" s="13" t="inlineStr">
+      <c r="I44" s="10" t="inlineStr">
         <is>
           <t>entry 값이 경로별로 다르게 남음 · programId 채워짐</t>
         </is>
       </c>
-      <c r="J44" s="13" t="inlineStr">
+      <c r="J44" s="10" t="inlineStr">
         <is>
           <t>IA-Q-06 · 개발 D-4</t>
         </is>
       </c>
-      <c r="K44" s="13" t="n"/>
+      <c r="K44" s="10" t="n"/>
       <c r="L44" s="17" t="inlineStr">
         <is>
           <t>보류</t>
@@ -4376,47 +4500,47 @@
           <t>P2</t>
         </is>
       </c>
-      <c r="C45" s="13" t="inlineStr">
+      <c r="C45" s="10" t="inlineStr">
         <is>
           <t>6 측정</t>
         </is>
       </c>
-      <c r="D45" s="13" t="inlineStr">
+      <c r="D45" s="10" t="inlineStr">
         <is>
           <t>이벤트</t>
         </is>
       </c>
-      <c r="E45" s="13" t="inlineStr">
+      <c r="E45" s="10" t="inlineStr">
         <is>
           <t>①</t>
         </is>
       </c>
-      <c r="F45" s="13" t="inlineStr">
+      <c r="F45" s="10" t="inlineStr">
         <is>
           <t>앱</t>
         </is>
       </c>
-      <c r="G45" s="13" t="inlineStr">
+      <c r="G45" s="10" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="H45" s="13" t="inlineStr">
+      <c r="H45" s="10" t="inlineStr">
         <is>
           <t>한 섹션에 30초 머문 뒤 이동</t>
         </is>
       </c>
-      <c r="I45" s="13" t="inlineStr">
+      <c r="I45" s="10" t="inlineStr">
         <is>
           <t>해당 섹션 dwell ≈ 30초</t>
         </is>
       </c>
-      <c r="J45" s="13" t="inlineStr">
+      <c r="J45" s="10" t="inlineStr">
         <is>
           <t>IA-Q-06</t>
         </is>
       </c>
-      <c r="K45" s="13" t="n"/>
+      <c r="K45" s="10" t="n"/>
       <c r="L45" s="17" t="inlineStr">
         <is>
           <t>통과</t>
@@ -4450,49 +4574,49 @@
           <t>P1</t>
         </is>
       </c>
-      <c r="C46" s="13" t="inlineStr">
+      <c r="C46" s="10" t="inlineStr">
         <is>
           <t>6 전화번호</t>
         </is>
       </c>
-      <c r="D46" s="13" t="inlineStr">
+      <c r="D46" s="10" t="inlineStr">
         <is>
           <t>전 화면</t>
         </is>
       </c>
-      <c r="E46" s="13" t="inlineStr">
+      <c r="E46" s="10" t="inlineStr">
         <is>
           <t>①</t>
         </is>
       </c>
-      <c r="F46" s="13" t="inlineStr">
+      <c r="F46" s="10" t="inlineStr">
         <is>
           <t>앱 · 웹 · 문자</t>
         </is>
       </c>
-      <c r="G46" s="13" t="inlineStr">
+      <c r="G46" s="10" t="inlineStr">
         <is>
           <t>개발 수정 반영 후</t>
         </is>
       </c>
-      <c r="H46" s="13" t="inlineStr">
+      <c r="H46" s="10" t="inlineStr">
         <is>
           <t>리포트 완료 · 실패 화면 · 신청폼 결과 화면 · 문자 본문의 번호</t>
         </is>
       </c>
-      <c r="I46" s="13" t="inlineStr">
+      <c r="I46" s="10" t="inlineStr">
         <is>
           <t>모두 032-453-6160 (6163 · 담당자 번호 없음)</t>
         </is>
       </c>
-      <c r="J46" s="13" t="inlineStr">
+      <c r="J46" s="10" t="inlineStr">
         <is>
           <t>K-14 · 보건소 요청 10/12</t>
         </is>
       </c>
       <c r="K46" s="16" t="inlineStr">
         <is>
-          <t>dev_08_done.png</t>
+          <t>cmp_08.png</t>
         </is>
       </c>
       <c r="L46" s="17" t="inlineStr">
@@ -4502,7 +4626,7 @@
       </c>
       <c r="M46" s="18" t="inlineStr">
         <is>
-          <t>완료 화면 032-453-6163 → BUG-05</t>
+          <t>완료 화면 032-453-6163 → BUG-01</t>
         </is>
       </c>
       <c r="N46" s="14" t="inlineStr">
@@ -4528,42 +4652,42 @@
           <t>P2</t>
         </is>
       </c>
-      <c r="C47" s="13" t="inlineStr">
+      <c r="C47" s="10" t="inlineStr">
         <is>
           <t>6 신청폼 4기</t>
         </is>
       </c>
-      <c r="D47" s="13" t="inlineStr">
+      <c r="D47" s="10" t="inlineStr">
         <is>
           <t>첫 화면</t>
         </is>
       </c>
-      <c r="E47" s="13" t="inlineStr">
+      <c r="E47" s="10" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="F47" s="13" t="inlineStr">
+      <c r="F47" s="10" t="inlineStr">
         <is>
           <t>휴대폰 브라우저</t>
         </is>
       </c>
-      <c r="G47" s="13" t="inlineStr">
+      <c r="G47" s="10" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="H47" s="13" t="inlineStr">
+      <c r="H47" s="10" t="inlineStr">
         <is>
           <t>/invitations/namdong4</t>
         </is>
       </c>
-      <c r="I47" s="13" t="inlineStr">
+      <c r="I47" s="10" t="inlineStr">
         <is>
           <t>명칭 · 기관명은 결정 Q-1 · Q-2대로 · "2027년 2월~11월"</t>
         </is>
       </c>
-      <c r="J47" s="13" t="inlineStr">
+      <c r="J47" s="10" t="inlineStr">
         <is>
           <t>개발 B-8</t>
         </is>
@@ -4606,42 +4730,42 @@
           <t>P1</t>
         </is>
       </c>
-      <c r="C48" s="13" t="inlineStr">
+      <c r="C48" s="10" t="inlineStr">
         <is>
           <t>6 신청폼 4기</t>
         </is>
       </c>
-      <c r="D48" s="13" t="inlineStr">
+      <c r="D48" s="10" t="inlineStr">
         <is>
           <t>입력 · 결과</t>
         </is>
       </c>
-      <c r="E48" s="13" t="inlineStr">
+      <c r="E48" s="10" t="inlineStr">
         <is>
           <t>본인 번호</t>
         </is>
       </c>
-      <c r="F48" s="13" t="inlineStr">
+      <c r="F48" s="10" t="inlineStr">
         <is>
           <t>휴대폰 브라우저</t>
         </is>
       </c>
-      <c r="G48" s="13" t="inlineStr">
+      <c r="G48" s="10" t="inlineStr">
         <is>
           <t>실제 문자 발송 — 본인 번호로 1회만</t>
         </is>
       </c>
-      <c r="H48" s="13" t="inlineStr">
+      <c r="H48" s="10" t="inlineStr">
         <is>
           <t>입력 폼 제출</t>
         </is>
       </c>
-      <c r="I48" s="13" t="inlineStr">
+      <c r="I48" s="10" t="inlineStr">
         <is>
           <t>결과 화면 문구 · 문자 내용 · 케어센터 신청자 관리에 1건</t>
         </is>
       </c>
-      <c r="J48" s="13" t="inlineStr">
+      <c r="J48" s="10" t="inlineStr">
         <is>
           <t>개발 B-8 · Q-3</t>
         </is>
@@ -4684,49 +4808,49 @@
           <t>P2</t>
         </is>
       </c>
-      <c r="C49" s="13" t="inlineStr">
+      <c r="C49" s="10" t="inlineStr">
         <is>
           <t>6 신청폼 4기</t>
         </is>
       </c>
-      <c r="D49" s="13" t="inlineStr">
+      <c r="D49" s="10" t="inlineStr">
         <is>
           <t>중복</t>
         </is>
       </c>
-      <c r="E49" s="13" t="inlineStr">
+      <c r="E49" s="10" t="inlineStr">
         <is>
           <t>본인 번호</t>
         </is>
       </c>
-      <c r="F49" s="13" t="inlineStr">
+      <c r="F49" s="10" t="inlineStr">
         <is>
           <t>휴대폰 브라우저</t>
         </is>
       </c>
-      <c r="G49" s="13" t="inlineStr">
+      <c r="G49" s="10" t="inlineStr">
         <is>
           <t>F-02 이후</t>
         </is>
       </c>
-      <c r="H49" s="13" t="inlineStr">
+      <c r="H49" s="10" t="inlineStr">
         <is>
           <t>같은 번호로 다시 제출</t>
         </is>
       </c>
-      <c r="I49" s="13" t="inlineStr">
+      <c r="I49" s="10" t="inlineStr">
         <is>
           <t>중복 안내 (정의 없음 → Q-4)</t>
         </is>
       </c>
-      <c r="J49" s="13" t="inlineStr">
+      <c r="J49" s="10" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="K49" s="13" t="n"/>
+      <c r="K49" s="10" t="n"/>
       <c r="L49" s="4" t="n"/>
-      <c r="M49" s="13" t="n"/>
+      <c r="M49" s="10" t="n"/>
       <c r="N49" s="14" t="inlineStr">
         <is>
           <t>미실행</t>
@@ -4750,49 +4874,49 @@
           <t>P3</t>
         </is>
       </c>
-      <c r="C50" s="13" t="inlineStr">
+      <c r="C50" s="10" t="inlineStr">
         <is>
           <t>6 신청폼 4기</t>
         </is>
       </c>
-      <c r="D50" s="13" t="inlineStr">
+      <c r="D50" s="10" t="inlineStr">
         <is>
           <t>대리 등록</t>
         </is>
       </c>
-      <c r="E50" s="13" t="inlineStr">
+      <c r="E50" s="10" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="F50" s="13" t="inlineStr">
+      <c r="F50" s="10" t="inlineStr">
         <is>
           <t>휴대폰 브라우저</t>
         </is>
       </c>
-      <c r="G50" s="13" t="inlineStr">
+      <c r="G50" s="10" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="H50" s="13" t="inlineStr">
+      <c r="H50" s="10" t="inlineStr">
         <is>
           <t>"보건소 직원이신가요?"</t>
         </is>
       </c>
-      <c r="I50" s="13" t="inlineStr">
+      <c r="I50" s="10" t="inlineStr">
         <is>
           <t>대리 등록 경로가 열림 (제출하지 않음)</t>
         </is>
       </c>
-      <c r="J50" s="13" t="inlineStr">
+      <c r="J50" s="10" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="K50" s="13" t="n"/>
+      <c r="K50" s="10" t="n"/>
       <c r="L50" s="4" t="n"/>
-      <c r="M50" s="13" t="n"/>
+      <c r="M50" s="10" t="n"/>
       <c r="N50" s="14" t="inlineStr">
         <is>
           <t>미실행</t>
@@ -4816,42 +4940,42 @@
           <t>P2</t>
         </is>
       </c>
-      <c r="C51" s="13" t="inlineStr">
+      <c r="C51" s="10" t="inlineStr">
         <is>
           <t>6 신청폼 3기</t>
         </is>
       </c>
-      <c r="D51" s="13" t="inlineStr">
+      <c r="D51" s="10" t="inlineStr">
         <is>
           <t>3기 링크</t>
         </is>
       </c>
-      <c r="E51" s="13" t="inlineStr">
+      <c r="E51" s="10" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="F51" s="13" t="inlineStr">
+      <c r="F51" s="10" t="inlineStr">
         <is>
           <t>휴대폰 브라우저</t>
         </is>
       </c>
-      <c r="G51" s="13" t="inlineStr">
+      <c r="G51" s="10" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="H51" s="13" t="inlineStr">
+      <c r="H51" s="10" t="inlineStr">
         <is>
           <t>/invitations/namdong3</t>
         </is>
       </c>
-      <c r="I51" s="13" t="inlineStr">
+      <c r="I51" s="10" t="inlineStr">
         <is>
           <t>결정 Q-6대로</t>
         </is>
       </c>
-      <c r="J51" s="13" t="inlineStr">
+      <c r="J51" s="10" t="inlineStr">
         <is>
           <t>개발 §A ⑤</t>
         </is>
@@ -4894,49 +5018,49 @@
           <t>P2</t>
         </is>
       </c>
-      <c r="C52" s="13" t="inlineStr">
+      <c r="C52" s="10" t="inlineStr">
         <is>
           <t>6 케어센터</t>
         </is>
       </c>
-      <c r="D52" s="13" t="inlineStr">
+      <c r="D52" s="10" t="inlineStr">
         <is>
           <t>4기</t>
         </is>
       </c>
-      <c r="E52" s="13" t="inlineStr">
+      <c r="E52" s="10" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="F52" s="13" t="inlineStr">
+      <c r="F52" s="10" t="inlineStr">
         <is>
           <t>PC</t>
         </is>
       </c>
-      <c r="G52" s="13" t="inlineStr">
+      <c r="G52" s="10" t="inlineStr">
         <is>
           <t>로그인</t>
         </is>
       </c>
-      <c r="H52" s="13" t="inlineStr">
+      <c r="H52" s="10" t="inlineStr">
         <is>
           <t>목록 · 신청자 관리</t>
         </is>
       </c>
-      <c r="I52" s="13" t="inlineStr">
+      <c r="I52" s="10" t="inlineStr">
         <is>
           <t>4기 "진행 예정" · 신청자 관리 탭 열림</t>
         </is>
       </c>
-      <c r="J52" s="13" t="inlineStr">
+      <c r="J52" s="10" t="inlineStr">
         <is>
           <t>개발 B-9</t>
         </is>
       </c>
-      <c r="K52" s="13" t="n"/>
+      <c r="K52" s="10" t="n"/>
       <c r="L52" s="4" t="n"/>
-      <c r="M52" s="13" t="n"/>
+      <c r="M52" s="10" t="n"/>
       <c r="N52" s="14" t="inlineStr">
         <is>
           <t>미실행</t>
@@ -5021,7 +5145,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N8"/>
+  <dimension ref="A1:N12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="9" customWidth="1" min="1" max="1"/>
@@ -5078,7 +5202,7 @@
       </c>
       <c r="H1" s="3" t="inlineStr">
         <is>
-          <t>기대 결과(정본)</t>
+          <t>기대 결과(피그마)</t>
         </is>
       </c>
       <c r="I1" s="3" t="inlineStr">
@@ -5118,9 +5242,9 @@
           <t>BUG-01</t>
         </is>
       </c>
-      <c r="B2" s="13" t="inlineStr">
-        <is>
-          <t>4기 신청 완료 본문 첫 줄 누락</t>
+      <c r="B2" s="10" t="inlineStr">
+        <is>
+          <t>문의 전화번호 6163 → 대표번호 6160</t>
         </is>
       </c>
       <c r="C2" s="4" t="inlineStr">
@@ -5135,47 +5259,47 @@
       </c>
       <c r="E2" s="14" t="inlineStr">
         <is>
-          <t>기획 선행</t>
-        </is>
-      </c>
-      <c r="F2" s="13" t="inlineStr">
-        <is>
-          <t>SC-RP-08 완료</t>
-        </is>
-      </c>
-      <c r="G2" s="13" t="inlineStr">
+          <t>개발 수정</t>
+        </is>
+      </c>
+      <c r="F2" s="10" t="inlineStr">
+        <is>
+          <t>SC-RP-08 완료 · 실패 · 신청폼 · 문자</t>
+        </is>
+      </c>
+      <c r="G2" s="10" t="inlineStr">
         <is>
           <t>https://dev-meli-web.meli.health/report-3gi?state=nice → 4기도 참여하기 → 네, 신청합니다</t>
         </is>
       </c>
-      <c r="H2" s="13" t="inlineStr">
-        <is>
-          <t>4줄: 4기가 시작될 때 보건소에서 / 연락드리겠습니다. / 자세한 문의사항은 032-453-6160으로 / 문의 바랍니다. 감사합니다.</t>
-        </is>
-      </c>
-      <c r="I2" s="13" t="inlineStr">
-        <is>
-          <t>2줄: 자세한 문의사항은 032-453-6163으로 / 문의 바랍니다. 감사합니다.</t>
+      <c r="H2" s="10" t="inlineStr">
+        <is>
+          <t>032-453-6160 (보건소 대표번호 · 10/12 확정 · 피그마 S8-05 디스크립션)</t>
+        </is>
+      </c>
+      <c r="I2" s="10" t="inlineStr">
+        <is>
+          <t>032-453-6163</t>
         </is>
       </c>
       <c r="J2" s="16" t="inlineStr">
         <is>
-          <t>cmp_08_done.png</t>
-        </is>
-      </c>
-      <c r="K2" s="13" t="inlineStr">
-        <is>
-          <t>S8-05 · 변경이력 29</t>
-        </is>
-      </c>
-      <c r="L2" s="13" t="inlineStr">
-        <is>
-          <t>기획(피그마 1463:1286 수정) → 개발</t>
-        </is>
-      </c>
-      <c r="M2" s="13" t="inlineStr">
-        <is>
-          <t>A-03</t>
+          <t>cmp_08.png</t>
+        </is>
+      </c>
+      <c r="K2" s="10" t="inlineStr">
+        <is>
+          <t>K-14 · 변경이력 39</t>
+        </is>
+      </c>
+      <c r="L2" s="10" t="inlineStr">
+        <is>
+          <t>개발</t>
+        </is>
+      </c>
+      <c r="M2" s="10" t="inlineStr">
+        <is>
+          <t>PH-01 · A-03 · A-07</t>
         </is>
       </c>
       <c r="N2" s="15" t="n"/>
@@ -5186,62 +5310,62 @@
           <t>BUG-02</t>
         </is>
       </c>
-      <c r="B3" s="13" t="inlineStr">
-        <is>
-          <t>4기 신청 완료 화면 제목 · 프로그램명 위치 바뀜</t>
+      <c r="B3" s="10" t="inlineStr">
+        <is>
+          <t>4기 신청 완료 본문 첫 줄 누락</t>
         </is>
       </c>
       <c r="C3" s="4" t="inlineStr">
         <is>
-          <t>Minor</t>
+          <t>Major</t>
         </is>
       </c>
       <c r="D3" s="4" t="inlineStr">
         <is>
-          <t>P2</t>
+          <t>P1</t>
         </is>
       </c>
       <c r="E3" s="14" t="inlineStr">
         <is>
-          <t>확인 필요</t>
-        </is>
-      </c>
-      <c r="F3" s="13" t="inlineStr">
+          <t>기획 선행</t>
+        </is>
+      </c>
+      <c r="F3" s="10" t="inlineStr">
         <is>
           <t>SC-RP-08 완료</t>
         </is>
       </c>
-      <c r="G3" s="13" t="inlineStr">
+      <c r="G3" s="10" t="inlineStr">
         <is>
           <t>https://dev-meli-web.meli.health/report-3gi/apply?state=nice</t>
         </is>
       </c>
-      <c r="H3" s="13" t="inlineStr">
-        <is>
-          <t>배지 → "신청이 완료되었습니다."(카드 밖, 큰 글씨) → 카드(✓ · 프로그램명 · 본문)</t>
-        </is>
-      </c>
-      <c r="I3" s="13" t="inlineStr">
-        <is>
-          <t>배지 → 프로그램명(카드 밖) → 카드(✓ · "신청이 완료되었습니다." · 본문)</t>
+      <c r="H3" s="10" t="inlineStr">
+        <is>
+          <t>4줄: 4기가 시작될 때 보건소에서 / 연락드리겠습니다. / 자세한 문의사항은 032-453-6160으로 / 문의 바랍니다. 감사합니다. (피그마 S8-05 디스크립션)</t>
+        </is>
+      </c>
+      <c r="I3" s="10" t="inlineStr">
+        <is>
+          <t>2줄: 자세한 문의사항은 … 문의 바랍니다. 감사합니다. — 피그마 목업 카드(1463:1286)가 아직 2줄이라 개발이 목업을 따름</t>
         </is>
       </c>
       <c r="J3" s="16" t="inlineStr">
         <is>
-          <t>cmp_08_done.png</t>
-        </is>
-      </c>
-      <c r="K3" s="13" t="inlineStr">
-        <is>
-          <t>S8-01~05</t>
-        </is>
-      </c>
-      <c r="L3" s="13" t="inlineStr">
-        <is>
-          <t>기획(피그마 확인) → 개발</t>
-        </is>
-      </c>
-      <c r="M3" s="13" t="inlineStr">
+          <t>cmp_08.png</t>
+        </is>
+      </c>
+      <c r="K3" s="10" t="inlineStr">
+        <is>
+          <t>S8-05 · FIG-01</t>
+        </is>
+      </c>
+      <c r="L3" s="10" t="inlineStr">
+        <is>
+          <t>기획(피그마 목업 수정) → 개발</t>
+        </is>
+      </c>
+      <c r="M3" s="10" t="inlineStr">
         <is>
           <t>A-03</t>
         </is>
@@ -5254,9 +5378,9 @@
           <t>BUG-03</t>
         </is>
       </c>
-      <c r="B4" s="13" t="inlineStr">
-        <is>
-          <t>표지 배지 문구 다름</t>
+      <c r="B4" s="10" t="inlineStr">
+        <is>
+          <t>표지 정렬 · 히어로 그래픽이 목업과 다름</t>
         </is>
       </c>
       <c r="C4" s="4" t="inlineStr">
@@ -5274,42 +5398,42 @@
           <t>확인 필요</t>
         </is>
       </c>
-      <c r="F4" s="13" t="inlineStr">
+      <c r="F4" s="10" t="inlineStr">
         <is>
           <t>SC-RP-01 표지</t>
         </is>
       </c>
-      <c r="G4" s="13" t="inlineStr">
+      <c r="G4" s="10" t="inlineStr">
         <is>
           <t>https://dev-meli-web.meli.health/report-3gi?state=nice 첫 화면</t>
         </is>
       </c>
-      <c r="H4" s="13" t="inlineStr">
-        <is>
-          <t>"2026 맬리브레인 3기"</t>
-        </is>
-      </c>
-      <c r="I4" s="13" t="inlineStr">
-        <is>
-          <t>"2026 인천 남동구 보건소 치매 예방 3기"</t>
+      <c r="H4" s="10" t="inlineStr">
+        <is>
+          <t>배지 · 이름 · 기간 왼쪽 정렬 / 캐릭터 뒤 메달(리본 + 원형 배경)</t>
+        </is>
+      </c>
+      <c r="I4" s="10" t="inlineStr">
+        <is>
+          <t>가운데 정렬 / 메달 없이 캐릭터만</t>
         </is>
       </c>
       <c r="J4" s="16" t="inlineStr">
         <is>
-          <t>cmp_01_cover.png</t>
-        </is>
-      </c>
-      <c r="K4" s="13" t="inlineStr">
-        <is>
-          <t>S1-01</t>
-        </is>
-      </c>
-      <c r="L4" s="13" t="inlineStr">
-        <is>
-          <t>기획(피그마 확인) → 개발</t>
-        </is>
-      </c>
-      <c r="M4" s="13" t="inlineStr">
+          <t>cmp_01.png</t>
+        </is>
+      </c>
+      <c r="K4" s="10" t="inlineStr">
+        <is>
+          <t>SC-RP-01 목업 1097:791 · Q-11</t>
+        </is>
+      </c>
+      <c r="L4" s="10" t="inlineStr">
+        <is>
+          <t>개발 (메달은 10/13 3D 에셋 확인 후)</t>
+        </is>
+      </c>
+      <c r="M4" s="10" t="inlineStr">
         <is>
           <t>S-01</t>
         </is>
@@ -5322,14 +5446,14 @@
           <t>BUG-04</t>
         </is>
       </c>
-      <c r="B5" s="13" t="inlineStr">
-        <is>
-          <t>표지 이름 뒤 띄어쓰기 없음</t>
+      <c r="B5" s="10" t="inlineStr">
+        <is>
+          <t>뇌 점수 꺾은선이 거의 평평함</t>
         </is>
       </c>
       <c r="C5" s="4" t="inlineStr">
         <is>
-          <t>Trivial</t>
+          <t>Minor</t>
         </is>
       </c>
       <c r="D5" s="4" t="inlineStr">
@@ -5342,44 +5466,44 @@
           <t>개발 수정</t>
         </is>
       </c>
-      <c r="F5" s="13" t="inlineStr">
-        <is>
-          <t>SC-RP-01 표지</t>
-        </is>
-      </c>
-      <c r="G5" s="13" t="inlineStr">
-        <is>
-          <t>https://dev-meli-web.meli.health/report-3gi?state=nice 첫 화면</t>
-        </is>
-      </c>
-      <c r="H5" s="13" t="inlineStr">
-        <is>
-          <t>"김*리 님,"</t>
-        </is>
-      </c>
-      <c r="I5" s="13" t="inlineStr">
-        <is>
-          <t>"김*리님,"</t>
+      <c r="F5" s="10" t="inlineStr">
+        <is>
+          <t>SC-RP-02</t>
+        </is>
+      </c>
+      <c r="G5" s="10" t="inlineStr">
+        <is>
+          <t>https://dev-meli-web.meli.health/report-3gi?state=nice 두 번째 화면</t>
+        </is>
+      </c>
+      <c r="H5" s="10" t="inlineStr">
+        <is>
+          <t>69점 → 77점이 눈에 띄게 올라가는 선 · 10월 라벨 강조 (목업)</t>
+        </is>
+      </c>
+      <c r="I5" s="10" t="inlineStr">
+        <is>
+          <t>시작과 끝이 거의 수평 · 10월 라벨 강조 없음</t>
         </is>
       </c>
       <c r="J5" s="16" t="inlineStr">
         <is>
-          <t>cmp_01_cover.png</t>
-        </is>
-      </c>
-      <c r="K5" s="13" t="inlineStr">
-        <is>
-          <t>S1-02</t>
-        </is>
-      </c>
-      <c r="L5" s="13" t="inlineStr">
+          <t>cmp_02.png</t>
+        </is>
+      </c>
+      <c r="K5" s="10" t="inlineStr">
+        <is>
+          <t>S2-05</t>
+        </is>
+      </c>
+      <c r="L5" s="10" t="inlineStr">
         <is>
           <t>개발</t>
         </is>
       </c>
-      <c r="M5" s="13" t="inlineStr">
-        <is>
-          <t>S-01</t>
+      <c r="M5" s="10" t="inlineStr">
+        <is>
+          <t>S-02</t>
         </is>
       </c>
       <c r="N5" s="15" t="n"/>
@@ -5390,70 +5514,342 @@
           <t>BUG-05</t>
         </is>
       </c>
-      <c r="B6" s="13" t="inlineStr">
-        <is>
-          <t>문의 전화번호 6163 → 대표번호 6160</t>
+      <c r="B6" s="10" t="inlineStr">
+        <is>
+          <t>요일 퍼센트 강조색 · 개인화 멘트 카드가 목업과 다름</t>
         </is>
       </c>
       <c r="C6" s="4" t="inlineStr">
         <is>
-          <t>Major</t>
+          <t>Minor</t>
         </is>
       </c>
       <c r="D6" s="4" t="inlineStr">
         <is>
-          <t>P1</t>
+          <t>P2</t>
         </is>
       </c>
       <c r="E6" s="14" t="inlineStr">
         <is>
+          <t>확인 필요</t>
+        </is>
+      </c>
+      <c r="F6" s="10" t="inlineStr">
+        <is>
+          <t>SC-RP-03</t>
+        </is>
+      </c>
+      <c r="G6" s="10" t="inlineStr">
+        <is>
+          <t>https://dev-meli-web.meli.health/report-3gi?state=nice 세 번째 화면</t>
+        </is>
+      </c>
+      <c r="H6" s="10" t="inlineStr">
+        <is>
+          <t>최다 요일 퍼센트(88%) 녹색 / 멘트 카드는 원형 캐릭터 없이 헤드라인 1줄 (목업)</t>
+        </is>
+      </c>
+      <c r="I6" s="10" t="inlineStr">
+        <is>
+          <t>88% 검정 / 왼쪽에 회색 원(캐릭터 자리) + 헤드라인 2줄로 줄바꿈</t>
+        </is>
+      </c>
+      <c r="J6" s="16" t="inlineStr">
+        <is>
+          <t>cmp_03.png</t>
+        </is>
+      </c>
+      <c r="K6" s="10" t="inlineStr">
+        <is>
+          <t>S3-06 · S3-08 · FIG-05</t>
+        </is>
+      </c>
+      <c r="L6" s="10" t="inlineStr">
+        <is>
+          <t>개발 (원형 캐릭터는 FIG-05 결정 후)</t>
+        </is>
+      </c>
+      <c r="M6" s="10" t="inlineStr">
+        <is>
+          <t>S-03</t>
+        </is>
+      </c>
+      <c r="N6" s="15" t="n"/>
+    </row>
+    <row r="7" ht="60" customHeight="1">
+      <c r="A7" s="4" t="inlineStr">
+        <is>
+          <t>BUG-06</t>
+        </is>
+      </c>
+      <c r="B7" s="10" t="inlineStr">
+        <is>
+          <t>증서 테두리 장식 없음</t>
+        </is>
+      </c>
+      <c r="C7" s="4" t="inlineStr">
+        <is>
+          <t>Minor</t>
+        </is>
+      </c>
+      <c r="D7" s="4" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="E7" s="14" t="inlineStr">
+        <is>
           <t>개발 수정</t>
         </is>
       </c>
-      <c r="F6" s="13" t="inlineStr">
-        <is>
-          <t>SC-RP-08 완료 · 실패 · 신청폼 · 문자</t>
-        </is>
-      </c>
-      <c r="G6" s="13" t="inlineStr">
-        <is>
-          <t>https://dev-meli-web.meli.health/report-3gi?state=nice → 4기 신청 완료 화면</t>
-        </is>
-      </c>
-      <c r="H6" s="13" t="inlineStr">
-        <is>
-          <t>032-453-6160 (보건소 대표번호 · 10/12 확정)</t>
-        </is>
-      </c>
-      <c r="I6" s="13" t="inlineStr">
-        <is>
-          <t>032-453-6163</t>
-        </is>
-      </c>
-      <c r="J6" s="16" t="inlineStr">
-        <is>
-          <t>dev_08_done.png</t>
-        </is>
-      </c>
-      <c r="K6" s="13" t="inlineStr">
-        <is>
-          <t>K-14 · 변경이력 39</t>
-        </is>
-      </c>
-      <c r="L6" s="13" t="inlineStr">
+      <c r="F7" s="10" t="inlineStr">
+        <is>
+          <t>SC-RP-07 A · B · C</t>
+        </is>
+      </c>
+      <c r="G7" s="10" t="inlineStr">
+        <is>
+          <t>https://dev-meli-web.meli.health/report-3gi?state=nice 마지막 화면</t>
+        </is>
+      </c>
+      <c r="H7" s="10" t="inlineStr">
+        <is>
+          <t>금박 테두리 + 이중 내부 라인 + 마름모 6개 (S7-04)</t>
+        </is>
+      </c>
+      <c r="I7" s="10" t="inlineStr">
+        <is>
+          <t>금박 테두리만 · 내부 라인 · 마름모 없음</t>
+        </is>
+      </c>
+      <c r="J7" s="16" t="inlineStr">
+        <is>
+          <t>cmp_07A.png</t>
+        </is>
+      </c>
+      <c r="K7" s="10" t="inlineStr">
+        <is>
+          <t>S7-04</t>
+        </is>
+      </c>
+      <c r="L7" s="10" t="inlineStr">
         <is>
           <t>개발</t>
         </is>
       </c>
-      <c r="M6" s="13" t="inlineStr">
-        <is>
-          <t>PH-01 · A-03 · A-07</t>
-        </is>
-      </c>
-      <c r="N6" s="15" t="n"/>
-    </row>
-    <row r="8">
-      <c r="A8" s="2" t="inlineStr">
+      <c r="M7" s="10" t="inlineStr">
+        <is>
+          <t>C-01 · C-04</t>
+        </is>
+      </c>
+      <c r="N7" s="15" t="n"/>
+    </row>
+    <row r="8" ht="60" customHeight="1">
+      <c r="A8" s="4" t="inlineStr">
+        <is>
+          <t>BUG-07</t>
+        </is>
+      </c>
+      <c r="B8" s="10" t="inlineStr">
+        <is>
+          <t>비대상 화면 아이콘 · 버튼 배치가 목업과 다름</t>
+        </is>
+      </c>
+      <c r="C8" s="4" t="inlineStr">
+        <is>
+          <t>Minor</t>
+        </is>
+      </c>
+      <c r="D8" s="4" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="E8" s="14" t="inlineStr">
+        <is>
+          <t>확인 필요</t>
+        </is>
+      </c>
+      <c r="F8" s="10" t="inlineStr">
+        <is>
+          <t>SYS-05 (P20)</t>
+        </is>
+      </c>
+      <c r="G8" s="10" t="inlineStr">
+        <is>
+          <t>https://dev-meli-web.meli.health/report-3gi?state=sys05</t>
+        </is>
+      </c>
+      <c r="H8" s="10" t="inlineStr">
+        <is>
+          <t>본문 위 원형 아이콘 · [홈으로 돌아가기]는 하단 전체 폭 흰 버튼 (목업 1136:5858)</t>
+        </is>
+      </c>
+      <c r="I8" s="10" t="inlineStr">
+        <is>
+          <t>아이콘 없음 · 버튼이 본문 바로 아래 좁은 회색 버튼</t>
+        </is>
+      </c>
+      <c r="J8" s="16" t="inlineStr">
+        <is>
+          <t>cmp_sys05.png</t>
+        </is>
+      </c>
+      <c r="K8" s="10" t="inlineStr">
+        <is>
+          <t>P20 · FIG-08</t>
+        </is>
+      </c>
+      <c r="L8" s="10" t="inlineStr">
+        <is>
+          <t>기획(아이콘 확정) → 개발</t>
+        </is>
+      </c>
+      <c r="M8" s="10" t="inlineStr">
+        <is>
+          <t>E-08</t>
+        </is>
+      </c>
+      <c r="N8" s="15" t="n"/>
+    </row>
+    <row r="9" ht="60" customHeight="1">
+      <c r="A9" s="4" t="inlineStr">
+        <is>
+          <t>BUG-08</t>
+        </is>
+      </c>
+      <c r="B9" s="10" t="inlineStr">
+        <is>
+          <t>스크롤 힌트가 카드 하단을 가림</t>
+        </is>
+      </c>
+      <c r="C9" s="4" t="inlineStr">
+        <is>
+          <t>Minor</t>
+        </is>
+      </c>
+      <c r="D9" s="4" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="E9" s="14" t="inlineStr">
+        <is>
+          <t>앱 확인</t>
+        </is>
+      </c>
+      <c r="F9" s="10" t="inlineStr">
+        <is>
+          <t>SC-RP-04B · 05 · 06</t>
+        </is>
+      </c>
+      <c r="G9" s="10" t="inlineStr">
+        <is>
+          <t>https://dev-meli-web.meli.health/report-3gi?state=nice 04B · 05 화면 진입 직후</t>
+        </is>
+      </c>
+      <c r="H9" s="10" t="inlineStr">
+        <is>
+          <t>진입 직후만 하단 고정 · 본문을 가리지 않음 (S1-05 v3.2)</t>
+        </is>
+      </c>
+      <c r="I9" s="10" t="inlineStr">
+        <is>
+          <t>05 안내박스 마지막 줄 · 04B 하단 문구 위에 힌트가 겹침 (375×812)</t>
+        </is>
+      </c>
+      <c r="J9" s="16" t="inlineStr">
+        <is>
+          <t>cmp_05.png</t>
+        </is>
+      </c>
+      <c r="K9" s="10" t="inlineStr">
+        <is>
+          <t>S1-05 · FE-05</t>
+        </is>
+      </c>
+      <c r="L9" s="10" t="inlineStr">
+        <is>
+          <t>개발</t>
+        </is>
+      </c>
+      <c r="M9" s="10" t="inlineStr">
+        <is>
+          <t>S-08</t>
+        </is>
+      </c>
+      <c r="N9" s="15" t="n"/>
+    </row>
+    <row r="10" ht="60" customHeight="1">
+      <c r="A10" s="4" t="inlineStr">
+        <is>
+          <t>BUG-09</t>
+        </is>
+      </c>
+      <c r="B10" s="10" t="inlineStr">
+        <is>
+          <t>TOP 3 게임명 줄바꿈 · 게이지 라벨 위치</t>
+        </is>
+      </c>
+      <c r="C10" s="4" t="inlineStr">
+        <is>
+          <t>Trivial</t>
+        </is>
+      </c>
+      <c r="D10" s="4" t="inlineStr">
+        <is>
+          <t>P3</t>
+        </is>
+      </c>
+      <c r="E10" s="14" t="inlineStr">
+        <is>
+          <t>확인 필요</t>
+        </is>
+      </c>
+      <c r="F10" s="10" t="inlineStr">
+        <is>
+          <t>SC-RP-04 · 05</t>
+        </is>
+      </c>
+      <c r="G10" s="10" t="inlineStr">
+        <is>
+          <t>https://dev-meli-web.meli.health/report-3gi?state=nice 04 · 05 화면</t>
+        </is>
+      </c>
+      <c r="H10" s="10" t="inlineStr">
+        <is>
+          <t>"재밌는 숫자 퍼즐 9X9" 한 줄 / 게이지 "양호" "위험" 라벨이 아크 옆 (목업)</t>
+        </is>
+      </c>
+      <c r="I10" s="10" t="inlineStr">
+        <is>
+          <t>게임명 2줄 / 라벨이 아크 끝 아래</t>
+        </is>
+      </c>
+      <c r="J10" s="16" t="inlineStr">
+        <is>
+          <t>cmp_04.png</t>
+        </is>
+      </c>
+      <c r="K10" s="10" t="inlineStr">
+        <is>
+          <t>S4-06 · S5-04</t>
+        </is>
+      </c>
+      <c r="L10" s="10" t="inlineStr">
+        <is>
+          <t>개발</t>
+        </is>
+      </c>
+      <c r="M10" s="10" t="inlineStr">
+        <is>
+          <t>S-04 · S-06</t>
+        </is>
+      </c>
+      <c r="N10" s="15" t="n"/>
+    </row>
+    <row r="12">
+      <c r="A12" s="2" t="inlineStr">
         <is>
           <t>새 결함은 아래 빈 행에 BUG-06부터 이어서 적습니다. 심각도: Blocker 사용 불가 · Major 잘못된 정보 · Minor 정본과 다름 · Trivial 표기</t>
         </is>
@@ -5475,12 +5871,432 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J4" r:id="rId3"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J5" r:id="rId4"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J10" r:id="rId9"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:H12"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="8" customWidth="1" min="1" max="1"/>
+    <col width="20" customWidth="1" min="2" max="2"/>
+    <col width="32" customWidth="1" min="3" max="3"/>
+    <col width="40" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="40" customWidth="1" min="6" max="6"/>
+    <col width="12" customWidth="1" min="7" max="7"/>
+    <col width="24" customWidth="1" min="8" max="8"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="3" t="inlineStr">
+        <is>
+          <t>ID</t>
+        </is>
+      </c>
+      <c r="B1" s="3" t="inlineStr">
+        <is>
+          <t>화면</t>
+        </is>
+      </c>
+      <c r="C1" s="3" t="inlineStr">
+        <is>
+          <t>목업</t>
+        </is>
+      </c>
+      <c r="D1" s="3" t="inlineStr">
+        <is>
+          <t>디스크립션</t>
+        </is>
+      </c>
+      <c r="E1" s="3" t="inlineStr">
+        <is>
+          <t>개발은 어느 쪽</t>
+        </is>
+      </c>
+      <c r="F1" s="3" t="inlineStr">
+        <is>
+          <t>제안</t>
+        </is>
+      </c>
+      <c r="G1" s="3" t="inlineStr">
+        <is>
+          <t>피그마 노드</t>
+        </is>
+      </c>
+      <c r="H1" s="3" t="inlineStr">
+        <is>
+          <t>처리 결과</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="54" customHeight="1">
+      <c r="A2" s="4" t="inlineStr">
+        <is>
+          <t>FIG-01</t>
+        </is>
+      </c>
+      <c r="B2" s="10" t="inlineStr">
+        <is>
+          <t>SC-RP-08 완료 본문</t>
+        </is>
+      </c>
+      <c r="C2" s="10" t="inlineStr">
+        <is>
+          <t>2줄 · {전화번호}</t>
+        </is>
+      </c>
+      <c r="D2" s="10" t="inlineStr">
+        <is>
+          <t>4줄 · 032-453-6160 (v3.2)</t>
+        </is>
+      </c>
+      <c r="E2" s="4" t="inlineStr">
+        <is>
+          <t>목업(2줄)</t>
+        </is>
+      </c>
+      <c r="F2" s="10" t="inlineStr">
+        <is>
+          <t>목업 카드를 4줄 · 6160으로 수정 (Pretendard 폰트라 피그마에서 직접)</t>
+        </is>
+      </c>
+      <c r="G2" s="4" t="inlineStr">
+        <is>
+          <t>1463:1286</t>
+        </is>
+      </c>
+      <c r="H2" s="15" t="n"/>
+    </row>
+    <row r="3" ht="54" customHeight="1">
+      <c r="A3" s="4" t="inlineStr">
+        <is>
+          <t>FIG-02</t>
+        </is>
+      </c>
+      <c r="B3" s="10" t="inlineStr">
+        <is>
+          <t>SC-RP-08 배치</t>
+        </is>
+      </c>
+      <c r="C3" s="10" t="inlineStr">
+        <is>
+          <t>배지 → 프로그램명 → 카드(✓ · 제목 · 본문)</t>
+        </is>
+      </c>
+      <c r="D3" s="10" t="inlineStr">
+        <is>
+          <t>S8-02 "배지 바로 아래 큰 제목"</t>
+        </is>
+      </c>
+      <c r="E3" s="4" t="inlineStr">
+        <is>
+          <t>목업</t>
+        </is>
+      </c>
+      <c r="F3" s="10" t="inlineStr">
+        <is>
+          <t>목업 유지 · 디스크립션 S8-02 문구만 "카드 안 큰 제목"으로 정정 (권장)</t>
+        </is>
+      </c>
+      <c r="G3" s="4" t="inlineStr">
+        <is>
+          <t>1484:1453</t>
+        </is>
+      </c>
+      <c r="H3" s="15" t="n"/>
+    </row>
+    <row r="4" ht="54" customHeight="1">
+      <c r="A4" s="4" t="inlineStr">
+        <is>
+          <t>FIG-03</t>
+        </is>
+      </c>
+      <c r="B4" s="10" t="inlineStr">
+        <is>
+          <t>08-a 실패 제목 · 프로그램명</t>
+        </is>
+      </c>
+      <c r="C4" s="10" t="inlineStr">
+        <is>
+          <t>"신청이 완료되지 못했습니다" · 프로그램명 없음</t>
+        </is>
+      </c>
+      <c r="D4" s="10" t="inlineStr">
+        <is>
+          <t>"신청하지 못했습니다." · S8-04 프로그램명 완료·실패 공통</t>
+        </is>
+      </c>
+      <c r="E4" s="4" t="inlineStr">
+        <is>
+          <t>확인 불가 (샘플 없음)</t>
+        </is>
+      </c>
+      <c r="F4" s="10" t="inlineStr">
+        <is>
+          <t>제목 하나로 확정 · 실패 화면 프로그램명 유무 확정</t>
+        </is>
+      </c>
+      <c r="G4" s="4" t="inlineStr">
+        <is>
+          <t>1461:6901</t>
+        </is>
+      </c>
+      <c r="H4" s="15" t="n"/>
+    </row>
+    <row r="5" ht="54" customHeight="1">
+      <c r="A5" s="4" t="inlineStr">
+        <is>
+          <t>FIG-04</t>
+        </is>
+      </c>
+      <c r="B5" s="10" t="inlineStr">
+        <is>
+          <t>SC-RP-01 배지</t>
+        </is>
+      </c>
+      <c r="C5" s="10" t="inlineStr">
+        <is>
+          <t>"2026 인천 남동구 보건소 치매 예방 3기"</t>
+        </is>
+      </c>
+      <c r="D5" s="10" t="inlineStr">
+        <is>
+          <t>S1-01 "2026년 인천 남동구 보건소 치매 예방 3기"</t>
+        </is>
+      </c>
+      <c r="E5" s="4" t="inlineStr">
+        <is>
+          <t>목업</t>
+        </is>
+      </c>
+      <c r="F5" s="10" t="inlineStr">
+        <is>
+          <t>"2026" / "2026년" 중 하나로 확정</t>
+        </is>
+      </c>
+      <c r="G5" s="4" t="inlineStr">
+        <is>
+          <t>1239:1351</t>
+        </is>
+      </c>
+      <c r="H5" s="15" t="n"/>
+    </row>
+    <row r="6" ht="54" customHeight="1">
+      <c r="A6" s="4" t="inlineStr">
+        <is>
+          <t>FIG-05</t>
+        </is>
+      </c>
+      <c r="B6" s="10" t="inlineStr">
+        <is>
+          <t>SC-RP-03 개인화 멘트</t>
+        </is>
+      </c>
+      <c r="C6" s="10" t="inlineStr">
+        <is>
+          <t>원형 캐릭터 없음 · 헤드라인 1줄</t>
+        </is>
+      </c>
+      <c r="D6" s="10" t="inlineStr">
+        <is>
+          <t>S3-08 "좌측 46px 원형 캐릭터 + 우측 2줄"</t>
+        </is>
+      </c>
+      <c r="E6" s="4" t="inlineStr">
+        <is>
+          <t>디스크립션(회색 원)</t>
+        </is>
+      </c>
+      <c r="F6" s="10" t="inlineStr">
+        <is>
+          <t>캐릭터를 넣을지 확정 — 넣으면 에셋 필요</t>
+        </is>
+      </c>
+      <c r="G6" s="4" t="inlineStr">
+        <is>
+          <t>1240:1351</t>
+        </is>
+      </c>
+      <c r="H6" s="15" t="n"/>
+    </row>
+    <row r="7" ht="54" customHeight="1">
+      <c r="A7" s="4" t="inlineStr">
+        <is>
+          <t>FIG-06</t>
+        </is>
+      </c>
+      <c r="B7" s="10" t="inlineStr">
+        <is>
+          <t>SC-RP-05 게이지 각도</t>
+        </is>
+      </c>
+      <c r="C7" s="10" t="inlineStr">
+        <is>
+          <t>반원에 가까운 아크</t>
+        </is>
+      </c>
+      <c r="D7" s="10" t="inlineStr">
+        <is>
+          <t>S5-04 "145° → 20° (125°)" · S5-05 "145 − 점수 × 8.333" (v2 값)</t>
+        </is>
+      </c>
+      <c r="E7" s="4" t="inlineStr">
+        <is>
+          <t>180° 반원</t>
+        </is>
+      </c>
+      <c r="F7" s="10" t="inlineStr">
+        <is>
+          <t>디스크립션을 정본 v3.0 "180° · 180 − 점수 × 12"로 정정</t>
+        </is>
+      </c>
+      <c r="G7" s="4" t="inlineStr">
+        <is>
+          <t>1239:1965</t>
+        </is>
+      </c>
+      <c r="H7" s="15" t="n"/>
+    </row>
+    <row r="8" ht="54" customHeight="1">
+      <c r="A8" s="4" t="inlineStr">
+        <is>
+          <t>FIG-07</t>
+        </is>
+      </c>
+      <c r="B8" s="10" t="inlineStr">
+        <is>
+          <t>SC-RP-07 인장</t>
+        </is>
+      </c>
+      <c r="C8" s="10" t="inlineStr">
+        <is>
+          <t>둥근 사각 · 기울어짐</t>
+        </is>
+      </c>
+      <c r="D8" s="10" t="inlineStr">
+        <is>
+          <t>S7-13 "48×48 원형 인장"</t>
+        </is>
+      </c>
+      <c r="E8" s="4" t="inlineStr">
+        <is>
+          <t>목업</t>
+        </is>
+      </c>
+      <c r="F8" s="10" t="inlineStr">
+        <is>
+          <t>목업 유지 · 디스크립션을 "둥근 사각"으로 정정 (권장)</t>
+        </is>
+      </c>
+      <c r="G8" s="4" t="inlineStr">
+        <is>
+          <t>1264:1433</t>
+        </is>
+      </c>
+      <c r="H8" s="15" t="n"/>
+    </row>
+    <row r="9" ht="54" customHeight="1">
+      <c r="A9" s="4" t="inlineStr">
+        <is>
+          <t>FIG-08</t>
+        </is>
+      </c>
+      <c r="B9" s="10" t="inlineStr">
+        <is>
+          <t>SYS-05 아이콘</t>
+        </is>
+      </c>
+      <c r="C9" s="10" t="inlineStr">
+        <is>
+          <t>회색 원(아이콘 자리)</t>
+        </is>
+      </c>
+      <c r="D9" s="10" t="inlineStr">
+        <is>
+          <t>P20 "제목 없이 본문 + 버튼" (아이콘 언급 없음)</t>
+        </is>
+      </c>
+      <c r="E9" s="4" t="inlineStr">
+        <is>
+          <t>아이콘 없음</t>
+        </is>
+      </c>
+      <c r="F9" s="10" t="inlineStr">
+        <is>
+          <t>아이콘을 넣을지 확정 — 넣으면 에셋 필요</t>
+        </is>
+      </c>
+      <c r="G9" s="4" t="inlineStr">
+        <is>
+          <t>1136:5858</t>
+        </is>
+      </c>
+      <c r="H9" s="15" t="n"/>
+    </row>
+    <row r="10" ht="54" customHeight="1">
+      <c r="A10" s="4" t="inlineStr">
+        <is>
+          <t>FIG-09</t>
+        </is>
+      </c>
+      <c r="B10" s="10" t="inlineStr">
+        <is>
+          <t>SC-RP-02 참여율 샘플값</t>
+        </is>
+      </c>
+      <c r="C10" s="10" t="inlineStr">
+        <is>
+          <t>142일인데 69%</t>
+        </is>
+      </c>
+      <c r="D10" s="10" t="inlineStr">
+        <is>
+          <t>F-02: 142 ÷ 242 = 59%</t>
+        </is>
+      </c>
+      <c r="E10" s="4" t="inlineStr">
+        <is>
+          <t>59%</t>
+        </is>
+      </c>
+      <c r="F10" s="10" t="inlineStr">
+        <is>
+          <t>목업 샘플값을 59%로 정정 (표기 오류 · 개발 영향 없음)</t>
+        </is>
+      </c>
+      <c r="G10" s="4" t="inlineStr">
+        <is>
+          <t>1122:856</t>
+        </is>
+      </c>
+      <c r="H10" s="15" t="n"/>
+    </row>
+    <row r="12">
+      <c r="A12" s="2" t="inlineStr">
+        <is>
+          <t>피그마 안에서 목업과 디스크립션이 서로 다른 곳입니다. QA 기준이 피그마라서, 하나로 맞춘 뒤 개발에 알려야 합니다.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A1:H1"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -5547,17 +6363,17 @@
           <t>Q-1</t>
         </is>
       </c>
-      <c r="B2" s="13" t="inlineStr">
+      <c r="B2" s="10" t="inlineStr">
         <is>
           <t>4기 명칭이 화면마다 다름</t>
         </is>
       </c>
-      <c r="C2" s="13" t="inlineStr">
+      <c r="C2" s="10" t="inlineStr">
         <is>
           <t>리포트 완료 "2027년 인천 남동구 보건소 치매예방 프로그램 4기" · 리포트 시트 "…프로그램을"(4기 없음) · 신청폼 첫 화면 "치매예방교실 4기" · 입력 폼 "두뇌운동 치매예방교실 4기" · 케어센터 "두뇌운동 치매예방교실-27년"</t>
         </is>
       </c>
-      <c r="D2" s="13" t="inlineStr">
+      <c r="D2" s="10" t="inlineStr">
         <is>
           <t>대외 명칭 1개 확정 · 리포트 시트에 "4기" 추가(권장)</t>
         </is>
@@ -5569,7 +6385,7 @@
       </c>
       <c r="F2" s="15" t="n"/>
       <c r="G2" s="14" t="n"/>
-      <c r="H2" s="13" t="inlineStr">
+      <c r="H2" s="10" t="inlineStr">
         <is>
           <t>K-13 · 개발 §A ①</t>
         </is>
@@ -5581,17 +6397,17 @@
           <t>Q-2</t>
         </is>
       </c>
-      <c r="B3" s="13" t="inlineStr">
+      <c r="B3" s="10" t="inlineStr">
         <is>
           <t>기관명 두 가지</t>
         </is>
       </c>
-      <c r="C3" s="13" t="inlineStr">
+      <c r="C3" s="10" t="inlineStr">
         <is>
           <t>신청폼 첫 화면 "인천 남동구 보건소" · 입력 폼 배지 "인천 남동구 치매안심센터" · 증서 "인천남동구 보건소"</t>
         </is>
       </c>
-      <c r="D3" s="13" t="inlineStr">
+      <c r="D3" s="10" t="inlineStr">
         <is>
           <t>보건소 / 치매안심센터 중 하나, 띄어쓰기 포함</t>
         </is>
@@ -5603,7 +6419,7 @@
       </c>
       <c r="F3" s="15" t="n"/>
       <c r="G3" s="14" t="n"/>
-      <c r="H3" s="13" t="inlineStr">
+      <c r="H3" s="10" t="inlineStr">
         <is>
           <t>K-09 · 개발 §A ①</t>
         </is>
@@ -5615,17 +6431,17 @@
           <t>Q-3</t>
         </is>
       </c>
-      <c r="B4" s="13" t="inlineStr">
+      <c r="B4" s="10" t="inlineStr">
         <is>
           <t>신청폼 4기 즉시 승인</t>
         </is>
       </c>
-      <c r="C4" s="13" t="inlineStr">
+      <c r="C4" s="10" t="inlineStr">
         <is>
           <t>입력 폼 "신청하면 바로 참여가 확정되고, 앱 설치 안내 문자가 갑니다" · 신청폼 기획 v1.0(9/21)은 관리자 승인</t>
         </is>
       </c>
-      <c r="D4" s="13" t="inlineStr">
+      <c r="D4" s="10" t="inlineStr">
         <is>
           <t>즉시 승인 유지 / 승인 대기 · 4기 접수 시작일과 문자 문구</t>
         </is>
@@ -5637,7 +6453,7 @@
       </c>
       <c r="F4" s="15" t="n"/>
       <c r="G4" s="14" t="n"/>
-      <c r="H4" s="13" t="inlineStr">
+      <c r="H4" s="10" t="inlineStr">
         <is>
           <t>개발 D-2 · form 06 #1</t>
         </is>
@@ -5649,17 +6465,17 @@
           <t>Q-4</t>
         </is>
       </c>
-      <c r="B5" s="13" t="inlineStr">
+      <c r="B5" s="10" t="inlineStr">
         <is>
           <t>리포트 신청과 신청폼 신청 중복</t>
         </is>
       </c>
-      <c r="C5" s="13" t="inlineStr">
+      <c r="C5" s="10" t="inlineStr">
         <is>
           <t>기획상 두 경로 연결 없음 (리포트 = 의사만 저장 · 문자 없음)</t>
         </is>
       </c>
-      <c r="D5" s="13" t="inlineStr">
+      <c r="D5" s="10" t="inlineStr">
         <is>
           <t>중복 1건 처리 방식 · 리포트 신청자에게 4기 시작 문자 여부 · 명단 이관 A/B</t>
         </is>
@@ -5671,7 +6487,7 @@
       </c>
       <c r="F5" s="15" t="n"/>
       <c r="G5" s="14" t="n"/>
-      <c r="H5" s="13" t="inlineStr">
+      <c r="H5" s="10" t="inlineStr">
         <is>
           <t>개발 §A ④</t>
         </is>
@@ -5683,17 +6499,17 @@
           <t>Q-5</t>
         </is>
       </c>
-      <c r="B6" s="13" t="inlineStr">
+      <c r="B6" s="10" t="inlineStr">
         <is>
           <t>60세 이상 조건 검증</t>
         </is>
       </c>
-      <c r="C6" s="13" t="inlineStr">
+      <c r="C6" s="10" t="inlineStr">
         <is>
           <t>첫 화면에만 "60세 이상" 표기 · 입력 폼 검증 미확인</t>
         </is>
       </c>
-      <c r="D6" s="13" t="inlineStr">
+      <c r="D6" s="10" t="inlineStr">
         <is>
           <t>생년월일로 막음 / 받고 보건소가 거름</t>
         </is>
@@ -5705,7 +6521,7 @@
       </c>
       <c r="F6" s="15" t="n"/>
       <c r="G6" s="14" t="n"/>
-      <c r="H6" s="13" t="inlineStr">
+      <c r="H6" s="10" t="inlineStr">
         <is>
           <t>—</t>
         </is>
@@ -5717,17 +6533,17 @@
           <t>Q-6</t>
         </is>
       </c>
-      <c r="B7" s="13" t="inlineStr">
+      <c r="B7" s="10" t="inlineStr">
         <is>
           <t>3기 신청폼 링크</t>
         </is>
       </c>
-      <c r="C7" s="13" t="inlineStr">
+      <c r="C7" s="10" t="inlineStr">
         <is>
           <t>namdong3 열림 · 제출 시 3기로 접수</t>
         </is>
       </c>
-      <c r="D7" s="13" t="inlineStr">
+      <c r="D7" s="10" t="inlineStr">
         <is>
           <t>4기로 보냄 / 모집 종료 화면 / 그대로</t>
         </is>
@@ -5739,7 +6555,7 @@
       </c>
       <c r="F7" s="15" t="n"/>
       <c r="G7" s="14" t="n"/>
-      <c r="H7" s="13" t="inlineStr">
+      <c r="H7" s="10" t="inlineStr">
         <is>
           <t>개발 §A ⑤</t>
         </is>
@@ -5751,17 +6567,17 @@
           <t>Q-7</t>
         </is>
       </c>
-      <c r="B8" s="13" t="inlineStr">
+      <c r="B8" s="10" t="inlineStr">
         <is>
           <t>11/1 하루 안내 공백</t>
         </is>
       </c>
-      <c r="C8" s="13" t="inlineStr">
+      <c r="C8" s="10" t="inlineStr">
         <is>
           <t>10/31 종료 ~ 11/2 공개 사이 카드 · 안내 없음</t>
         </is>
       </c>
-      <c r="D8" s="13" t="inlineStr">
+      <c r="D8" s="10" t="inlineStr">
         <is>
           <t>그대로 / 11/1로 당김</t>
         </is>
@@ -5773,7 +6589,7 @@
       </c>
       <c r="F8" s="15" t="n"/>
       <c r="G8" s="14" t="n"/>
-      <c r="H8" s="13" t="inlineStr">
+      <c r="H8" s="10" t="inlineStr">
         <is>
           <t>개발 §A ②</t>
         </is>
@@ -5785,17 +6601,17 @@
           <t>Q-8</t>
         </is>
       </c>
-      <c r="B9" s="13" t="inlineStr">
+      <c r="B9" s="10" t="inlineStr">
         <is>
           <t>푸시 · 사전 안내 문구</t>
         </is>
       </c>
-      <c r="C9" s="13" t="inlineStr">
+      <c r="C9" s="10" t="inlineStr">
         <is>
           <t>미발송 기본값</t>
         </is>
       </c>
-      <c r="D9" s="13" t="inlineStr">
+      <c r="D9" s="10" t="inlineStr">
         <is>
           <t>보냄(문구) / 안 보냄</t>
         </is>
@@ -5807,7 +6623,7 @@
       </c>
       <c r="F9" s="15" t="n"/>
       <c r="G9" s="14" t="n"/>
-      <c r="H9" s="13" t="inlineStr">
+      <c r="H9" s="10" t="inlineStr">
         <is>
           <t>IA-Q-04 · IA-Q-05 · 개발 §A ⑥</t>
         </is>
@@ -5819,7 +6635,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -5878,17 +6694,17 @@
       <c r="A2" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="B2" s="13" t="inlineStr">
+      <c r="B2" s="10" t="inlineStr">
         <is>
           <t>등급별 인원 A / B / C (F-16 변경 전 · 후)</t>
         </is>
       </c>
-      <c r="C2" s="13" t="inlineStr">
+      <c r="C2" s="10" t="inlineStr">
         <is>
           <t>12명 B → A가 맞는지</t>
         </is>
       </c>
-      <c r="D2" s="13" t="inlineStr">
+      <c r="D2" s="10" t="inlineStr">
         <is>
           <t>S-02</t>
         </is>
@@ -5905,17 +6721,17 @@
       <c r="A3" s="4" t="n">
         <v>2</v>
       </c>
-      <c r="B3" s="13" t="inlineStr">
+      <c r="B3" s="10" t="inlineStr">
         <is>
           <t>B → A로 바뀐 12명 목록 (참여일 · 게임 횟수 · 판정 조건)</t>
         </is>
       </c>
-      <c r="C3" s="13" t="inlineStr">
+      <c r="C3" s="10" t="inlineStr">
         <is>
           <t>두 번째 조건 단독 발동 확인</t>
         </is>
       </c>
-      <c r="D3" s="13" t="inlineStr">
+      <c r="D3" s="10" t="inlineStr">
         <is>
           <t>S-02</t>
         </is>
@@ -5932,17 +6748,17 @@
       <c r="A4" s="4" t="n">
         <v>3</v>
       </c>
-      <c r="B4" s="13" t="inlineStr">
+      <c r="B4" s="10" t="inlineStr">
         <is>
           <t>판정 근거 로그 샘플 (조건 1 / 조건 2 / 둘 다)</t>
         </is>
       </c>
-      <c r="C4" s="13" t="inlineStr">
+      <c r="C4" s="10" t="inlineStr">
         <is>
           <t>K-06 · D-30</t>
         </is>
       </c>
-      <c r="D4" s="13" t="inlineStr">
+      <c r="D4" s="10" t="inlineStr">
         <is>
           <t>S-02</t>
         </is>
@@ -5959,17 +6775,17 @@
       <c r="A5" s="4" t="n">
         <v>4</v>
       </c>
-      <c r="B5" s="13" t="inlineStr">
+      <c r="B5" s="10" t="inlineStr">
         <is>
           <t>폼 동의 기록 없는 계정 목록 (55명) · 그중 리포트 대상 수</t>
         </is>
       </c>
-      <c r="C5" s="13" t="inlineStr">
+      <c r="C5" s="10" t="inlineStr">
         <is>
           <t>07-m 범위</t>
         </is>
       </c>
-      <c r="D5" s="13" t="inlineStr">
+      <c r="D5" s="10" t="inlineStr">
         <is>
           <t>A-09</t>
         </is>
@@ -5986,17 +6802,17 @@
       <c r="A6" s="4" t="n">
         <v>5</v>
       </c>
-      <c r="B6" s="13" t="inlineStr">
+      <c r="B6" s="10" t="inlineStr">
         <is>
           <t>테스트 계정 ①~④ 리포트 원값 (payload)</t>
         </is>
       </c>
-      <c r="C6" s="13" t="inlineStr">
+      <c r="C6" s="10" t="inlineStr">
         <is>
           <t>화면 숫자와 대조</t>
         </is>
       </c>
-      <c r="D6" s="13" t="inlineStr">
+      <c r="D6" s="10" t="inlineStr">
         <is>
           <t>S-02</t>
         </is>
@@ -6013,17 +6829,17 @@
       <c r="A7" s="4" t="n">
         <v>6</v>
       </c>
-      <c r="B7" s="13" t="inlineStr">
+      <c r="B7" s="10" t="inlineStr">
         <is>
           <t>4기 신청 의사 저장 테이블 구조 + dev 기록 (누가 · 언제)</t>
         </is>
       </c>
-      <c r="C7" s="13" t="inlineStr">
+      <c r="C7" s="10" t="inlineStr">
         <is>
           <t>명단 이관 (§A ④)</t>
         </is>
       </c>
-      <c r="D7" s="13" t="inlineStr">
+      <c r="D7" s="10" t="inlineStr">
         <is>
           <t>A-03 · A-06</t>
         </is>
@@ -6040,17 +6856,17 @@
       <c r="A8" s="4" t="n">
         <v>7</v>
       </c>
-      <c r="B8" s="13" t="inlineStr">
+      <c r="B8" s="10" t="inlineStr">
         <is>
           <t>측정 이벤트 집계 (섹션별 방문 수 · 방문자 수 · 평균 체류)</t>
         </is>
       </c>
-      <c r="C8" s="13" t="inlineStr">
+      <c r="C8" s="10" t="inlineStr">
         <is>
           <t>IA-Q-06</t>
         </is>
       </c>
-      <c r="D8" s="13" t="inlineStr">
+      <c r="D8" s="10" t="inlineStr">
         <is>
           <t>M-01 · M-02</t>
         </is>
@@ -6067,17 +6883,17 @@
       <c r="A9" s="4" t="n">
         <v>8</v>
       </c>
-      <c r="B9" s="13" t="inlineStr">
+      <c r="B9" s="10" t="inlineStr">
         <is>
           <t>실패 화면 샘플 주소 (state=08a) · 측정 1회 / 0회 · 걸음 미연동 계정</t>
         </is>
       </c>
-      <c r="C9" s="13" t="inlineStr">
+      <c r="C9" s="10" t="inlineStr">
         <is>
           <t>웹 샘플로 못 본 화면</t>
         </is>
       </c>
-      <c r="D9" s="13" t="inlineStr">
+      <c r="D9" s="10" t="inlineStr">
         <is>
           <t>A-07 · S-06 · S-07</t>
         </is>
@@ -6096,7 +6912,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -6152,22 +6968,22 @@
           <t>①</t>
         </is>
       </c>
-      <c r="B3" s="13" t="inlineStr">
+      <c r="B3" s="10" t="inlineStr">
         <is>
           <t>099-0002-8800</t>
         </is>
       </c>
-      <c r="C3" s="13" t="inlineStr">
+      <c r="C3" s="10" t="inlineStr">
         <is>
           <t>박용주</t>
         </is>
       </c>
-      <c r="D3" s="13" t="inlineStr">
+      <c r="D3" s="10" t="inlineStr">
         <is>
           <t>A 수료</t>
         </is>
       </c>
-      <c r="E3" s="13" t="inlineStr">
+      <c r="E3" s="10" t="inlineStr">
         <is>
           <t>첫 진입 · 자동 팝업 · 저장 · 4기 신청 전체</t>
         </is>
@@ -6179,22 +6995,22 @@
           <t>②</t>
         </is>
       </c>
-      <c r="B4" s="13" t="inlineStr">
+      <c r="B4" s="10" t="inlineStr">
         <is>
           <t>099-0002-1234</t>
         </is>
       </c>
-      <c r="C4" s="13" t="inlineStr">
+      <c r="C4" s="10" t="inlineStr">
         <is>
           <t>박희로</t>
         </is>
       </c>
-      <c r="D4" s="13" t="inlineStr">
+      <c r="D4" s="10" t="inlineStr">
         <is>
           <t>A · 4기 신청 완료</t>
         </is>
       </c>
-      <c r="E4" s="13" t="inlineStr">
+      <c r="E4" s="10" t="inlineStr">
         <is>
           <t>꽉 찬 데이터(게임 71회 · 마음 12일 · 1위) · 07-l</t>
         </is>
@@ -6206,22 +7022,22 @@
           <t>③</t>
         </is>
       </c>
-      <c r="B5" s="13" t="inlineStr">
+      <c r="B5" s="10" t="inlineStr">
         <is>
           <t>099-3333-3333</t>
         </is>
       </c>
-      <c r="C5" s="13" t="inlineStr">
+      <c r="C5" s="10" t="inlineStr">
         <is>
           <t>서비스</t>
         </is>
       </c>
-      <c r="D5" s="13" t="inlineStr">
+      <c r="D5" s="10" t="inlineStr">
         <is>
           <t>B 참여기록</t>
         </is>
       </c>
-      <c r="E5" s="13" t="inlineStr">
+      <c r="E5" s="10" t="inlineStr">
         <is>
           <t>참여기록 라벨 · 파일명</t>
         </is>
@@ -6233,22 +7049,22 @@
           <t>④</t>
         </is>
       </c>
-      <c r="B6" s="13" t="inlineStr">
+      <c r="B6" s="10" t="inlineStr">
         <is>
           <t>099-5555-5555</t>
         </is>
       </c>
-      <c r="C6" s="13" t="inlineStr">
+      <c r="C6" s="10" t="inlineStr">
         <is>
           <t>김철순</t>
         </is>
       </c>
-      <c r="D6" s="13" t="inlineStr">
+      <c r="D6" s="10" t="inlineStr">
         <is>
           <t>C 참여확인</t>
         </is>
       </c>
-      <c r="E6" s="13" t="inlineStr">
+      <c r="E6" s="10" t="inlineStr">
         <is>
           <t>저장 버튼 없음</t>
         </is>
@@ -6260,22 +7076,22 @@
           <t>⑤</t>
         </is>
       </c>
-      <c r="B7" s="13" t="inlineStr">
+      <c r="B7" s="10" t="inlineStr">
         <is>
           <t>099-0002-4096</t>
         </is>
       </c>
-      <c r="C7" s="13" t="inlineStr">
+      <c r="C7" s="10" t="inlineStr">
         <is>
           <t>김철순</t>
         </is>
       </c>
-      <c r="D7" s="13" t="inlineStr">
+      <c r="D7" s="10" t="inlineStr">
         <is>
           <t>A · 동의 기록 없음</t>
         </is>
       </c>
-      <c r="E7" s="13" t="inlineStr">
+      <c r="E7" s="10" t="inlineStr">
         <is>
           <t>다른 프로그램 진행 중 → 카드 없음 · 07-m 4기 버튼 숨김</t>
         </is>
@@ -6287,22 +7103,22 @@
           <t>⑥</t>
         </is>
       </c>
-      <c r="B8" s="13" t="inlineStr">
+      <c r="B8" s="10" t="inlineStr">
         <is>
           <t>099-0988-8888</t>
         </is>
       </c>
-      <c r="C8" s="13" t="inlineStr">
+      <c r="C8" s="10" t="inlineStr">
         <is>
           <t>안녕하세요</t>
         </is>
       </c>
-      <c r="D8" s="13" t="inlineStr">
+      <c r="D8" s="10" t="inlineStr">
         <is>
           <t>공개 전</t>
         </is>
       </c>
-      <c r="E8" s="13" t="inlineStr">
+      <c r="E8" s="10" t="inlineStr">
         <is>
           <t>카드 없음 · 링크로 열면 "아직 볼 수 없어요"</t>
         </is>
@@ -6314,22 +7130,22 @@
           <t>⑦</t>
         </is>
       </c>
-      <c r="B9" s="13" t="inlineStr">
+      <c r="B9" s="10" t="inlineStr">
         <is>
           <t>099-0008-9999</t>
         </is>
       </c>
-      <c r="C9" s="13" t="inlineStr">
+      <c r="C9" s="10" t="inlineStr">
         <is>
           <t>원메딕스</t>
         </is>
       </c>
-      <c r="D9" s="13" t="inlineStr">
+      <c r="D9" s="10" t="inlineStr">
         <is>
           <t>리포트 없음</t>
         </is>
       </c>
-      <c r="E9" s="13" t="inlineStr">
+      <c r="E9" s="10" t="inlineStr">
         <is>
           <t>카드 없음 · 링크로 열면 P20 비대상 안내</t>
         </is>
@@ -6343,51 +7159,51 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="13" t="inlineStr">
+      <c r="A12" s="10" t="inlineStr">
         <is>
           <t>P1</t>
         </is>
       </c>
-      <c r="B12" s="13" t="inlineStr">
+      <c r="B12" s="10" t="inlineStr">
         <is>
           <t>배포 차단</t>
         </is>
       </c>
-      <c r="C12" s="13" t="inlineStr">
+      <c r="C12" s="10" t="inlineStr">
         <is>
           <t>실패하면 배포하지 않습니다. 진입 · 저장 · 4기 신청 · 닫기 · 번호 · 비대상처럼 사용자가 막히거나 잘못된 정보를 받는 항목</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="13" t="inlineStr">
+      <c r="A13" s="10" t="inlineStr">
         <is>
           <t>P2</t>
         </is>
       </c>
-      <c r="B13" s="13" t="inlineStr">
+      <c r="B13" s="10" t="inlineStr">
         <is>
           <t>화면 · 문구</t>
         </is>
       </c>
-      <c r="C13" s="13" t="inlineStr">
+      <c r="C13" s="10" t="inlineStr">
         <is>
           <t>정본과 문구 · 숫자 · 배치가 같은지. 실패해도 배포는 가능하지만 출시 전 수정 대상</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="13" t="inlineStr">
+      <c r="A14" s="10" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
       </c>
-      <c r="B14" s="13" t="inlineStr">
+      <c r="B14" s="10" t="inlineStr">
         <is>
           <t>예외 · 환경</t>
         </is>
       </c>
-      <c r="C14" s="13" t="inlineStr">
+      <c r="C14" s="10" t="inlineStr">
         <is>
           <t>권한 거부 · 오프라인 · 작은 화면 · 큰 글씨 등 드문 상황. 출시 후 수정 가능</t>
         </is>
@@ -6401,60 +7217,60 @@
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="13" t="inlineStr">
+      <c r="A17" s="10" t="inlineStr">
         <is>
           <t>통과</t>
         </is>
       </c>
-      <c r="B17" s="13" t="inlineStr">
+      <c r="B17" s="10" t="inlineStr">
         <is>
           <t>기대 결과와 같음</t>
         </is>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="13" t="inlineStr">
+      <c r="A18" s="10" t="inlineStr">
         <is>
           <t>실패</t>
         </is>
       </c>
-      <c r="B18" s="13" t="inlineStr">
+      <c r="B18" s="10" t="inlineStr">
         <is>
           <t>다름 → 결함 시트에 BUG 번호로 적고 TC의 결함 ID 칸에 연결</t>
         </is>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="13" t="inlineStr">
+      <c r="A19" s="10" t="inlineStr">
         <is>
           <t>보류</t>
         </is>
       </c>
-      <c r="B19" s="13" t="inlineStr">
+      <c r="B19" s="10" t="inlineStr">
         <is>
           <t>판단에 결정 · 데이터가 더 필요</t>
         </is>
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="13" t="inlineStr">
+      <c r="A20" s="10" t="inlineStr">
         <is>
           <t>미실행</t>
         </is>
       </c>
-      <c r="B20" s="13" t="inlineStr">
+      <c r="B20" s="10" t="inlineStr">
         <is>
           <t>아직 안 함</t>
         </is>
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="13" t="inlineStr">
+      <c r="A21" s="10" t="inlineStr">
         <is>
           <t>해당없음</t>
         </is>
       </c>
-      <c r="B21" s="13" t="inlineStr">
+      <c r="B21" s="10" t="inlineStr">
         <is>
           <t>이 환경에서는 볼 수 없음</t>
         </is>
@@ -6468,7 +7284,7 @@
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="13" t="inlineStr">
+      <c r="A24" s="10" t="inlineStr">
         <is>
           <t>수료 A</t>
         </is>
@@ -6480,7 +7296,7 @@
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="13" t="inlineStr">
+      <c r="A25" s="10" t="inlineStr">
         <is>
           <t>참여기록 B</t>
         </is>
@@ -6492,7 +7308,7 @@
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="13" t="inlineStr">
+      <c r="A26" s="10" t="inlineStr">
         <is>
           <t>참여확인 C</t>
         </is>
@@ -6504,7 +7320,7 @@
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="13" t="inlineStr">
+      <c r="A27" s="10" t="inlineStr">
         <is>
           <t>4기 신청 완료</t>
         </is>
@@ -6516,7 +7332,7 @@
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="13" t="inlineStr">
+      <c r="A28" s="10" t="inlineStr">
         <is>
           <t>비대상 P20</t>
         </is>
@@ -6528,7 +7344,7 @@
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="13" t="inlineStr">
+      <c r="A29" s="10" t="inlineStr">
         <is>
           <t>신청폼 4기 (제출하면 실제 문자 — 본인 번호만)</t>
         </is>
@@ -6552,13 +7368,13 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q68"/>
+  <dimension ref="A1:H214"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="9" customWidth="1" min="1" max="1"/>
@@ -6590,137 +7406,197 @@
     <row r="1">
       <c r="A1" s="8" t="inlineStr">
         <is>
-          <t>웹 샘플 캡처 (2026-10-12 · 360×740) — 빨간 테두리 = 개발, 초록 테두리 = 기획 프로토타입</t>
+          <t>개발 dev(375×812, 빨강) vs 피그마 목업(초록) — 2026-10-12</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="8" t="inlineStr">
         <is>
-          <t>BUG-01 · 02 · 05 완료 화면 비교</t>
-        </is>
-      </c>
-      <c r="G3" s="8" t="inlineStr">
-        <is>
-          <t>BUG-03 · 04 표지 비교</t>
+          <t>SC-RP-01 표지 · BUG-03</t>
+        </is>
+      </c>
+      <c r="H3" s="8" t="inlineStr">
+        <is>
+          <t>SC-RP-02 · BUG-04</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="19" t="inlineStr">
         <is>
-          <t>cmp_08_done.png</t>
-        </is>
-      </c>
-      <c r="G4" s="19" t="inlineStr">
-        <is>
-          <t>cmp_01_cover.png</t>
-        </is>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" s="8" t="inlineStr">
-        <is>
-          <t>A-01 4기 확인 시트</t>
-        </is>
-      </c>
-      <c r="E35" s="8" t="inlineStr">
-        <is>
-          <t>A-05 07-l</t>
-        </is>
-      </c>
-      <c r="I35" s="8" t="inlineStr">
-        <is>
-          <t>C-01 증서 A</t>
-        </is>
-      </c>
-      <c r="M35" s="8" t="inlineStr">
-        <is>
-          <t>C-03 증서 B</t>
-        </is>
-      </c>
-      <c r="Q35" s="8" t="inlineStr">
-        <is>
-          <t>C-04 증서 C</t>
-        </is>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" s="19" t="inlineStr">
-        <is>
-          <t>dev_07h_sheet.png</t>
-        </is>
-      </c>
-      <c r="E36" s="19" t="inlineStr">
-        <is>
-          <t>dev_07_l.png</t>
-        </is>
-      </c>
-      <c r="I36" s="19" t="inlineStr">
-        <is>
-          <t>dev_07_A.png</t>
-        </is>
-      </c>
-      <c r="M36" s="19" t="inlineStr">
-        <is>
-          <t>dev_07_B.png</t>
-        </is>
-      </c>
-      <c r="Q36" s="19" t="inlineStr">
-        <is>
-          <t>dev_07_C.png</t>
-        </is>
-      </c>
-    </row>
-    <row r="67">
-      <c r="A67" s="8" t="inlineStr">
-        <is>
-          <t>E-08 비대상</t>
-        </is>
-      </c>
-      <c r="E67" s="8" t="inlineStr">
-        <is>
-          <t>S-05 · S-08 랭킹</t>
-        </is>
-      </c>
-      <c r="I67" s="8" t="inlineStr">
+          <t>cmp_01.png</t>
+        </is>
+      </c>
+      <c r="H4" s="19" t="inlineStr">
+        <is>
+          <t>cmp_02.png</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="8" t="inlineStr">
+        <is>
+          <t>SC-RP-03 · BUG-05</t>
+        </is>
+      </c>
+      <c r="H33" s="8" t="inlineStr">
+        <is>
+          <t>SC-RP-04 · BUG-09</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="19" t="inlineStr">
+        <is>
+          <t>cmp_03.png</t>
+        </is>
+      </c>
+      <c r="H34" s="19" t="inlineStr">
+        <is>
+          <t>cmp_04.png</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="8" t="inlineStr">
+        <is>
+          <t>SC-RP-04B</t>
+        </is>
+      </c>
+      <c r="H63" s="8" t="inlineStr">
+        <is>
+          <t>SC-RP-05 · BUG-08 · 09</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="19" t="inlineStr">
+        <is>
+          <t>cmp_04B.png</t>
+        </is>
+      </c>
+      <c r="H64" s="19" t="inlineStr">
+        <is>
+          <t>cmp_05.png</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" s="8" t="inlineStr">
+        <is>
+          <t>SC-RP-06</t>
+        </is>
+      </c>
+      <c r="H93" s="8" t="inlineStr">
+        <is>
+          <t>SC-RP-07 A · BUG-06</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" s="19" t="inlineStr">
+        <is>
+          <t>cmp_06.png</t>
+        </is>
+      </c>
+      <c r="H94" s="19" t="inlineStr">
+        <is>
+          <t>cmp_07A.png</t>
+        </is>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" s="8" t="inlineStr">
+        <is>
+          <t>SC-RP-07 B</t>
+        </is>
+      </c>
+      <c r="H123" s="8" t="inlineStr">
+        <is>
+          <t>SC-RP-07 C</t>
+        </is>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" s="19" t="inlineStr">
+        <is>
+          <t>cmp_07B.png</t>
+        </is>
+      </c>
+      <c r="H124" s="19" t="inlineStr">
+        <is>
+          <t>cmp_07C.png</t>
+        </is>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" s="8" t="inlineStr">
+        <is>
+          <t>07-h 시트</t>
+        </is>
+      </c>
+      <c r="H153" s="8" t="inlineStr">
+        <is>
+          <t>07-l</t>
+        </is>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" s="19" t="inlineStr">
+        <is>
+          <t>cmp_07h.png</t>
+        </is>
+      </c>
+      <c r="H154" s="19" t="inlineStr">
+        <is>
+          <t>cmp_07l.png</t>
+        </is>
+      </c>
+    </row>
+    <row r="183">
+      <c r="A183" s="8" t="inlineStr">
+        <is>
+          <t>SC-RP-08 · BUG-01 · 02</t>
+        </is>
+      </c>
+      <c r="H183" s="8" t="inlineStr">
+        <is>
+          <t>SYS-05 · BUG-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="184">
+      <c r="A184" s="19" t="inlineStr">
+        <is>
+          <t>cmp_08.png</t>
+        </is>
+      </c>
+      <c r="H184" s="19" t="inlineStr">
+        <is>
+          <t>cmp_sys05.png</t>
+        </is>
+      </c>
+    </row>
+    <row r="213">
+      <c r="A213" s="8" t="inlineStr">
         <is>
           <t>F-01 신청폼 4기 첫 화면</t>
         </is>
       </c>
-      <c r="M67" s="8" t="inlineStr">
-        <is>
-          <t>F-02 신청폼 4기 입력</t>
-        </is>
-      </c>
-      <c r="Q67" s="8" t="inlineStr">
+      <c r="H213" s="8" t="inlineStr">
         <is>
           <t>F-05 3기 링크</t>
         </is>
       </c>
     </row>
-    <row r="68">
-      <c r="A68" s="19" t="inlineStr">
-        <is>
-          <t>dev_P20.png</t>
-        </is>
-      </c>
-      <c r="E68" s="19" t="inlineStr">
-        <is>
-          <t>dev_04B.png</t>
-        </is>
-      </c>
-      <c r="I68" s="19" t="inlineStr">
+    <row r="214">
+      <c r="A214" s="19" t="inlineStr">
         <is>
           <t>dev_form4_landing.png</t>
         </is>
       </c>
-      <c r="M68" s="19" t="inlineStr">
-        <is>
-          <t>dev_form4_form.png</t>
-        </is>
-      </c>
-      <c r="Q68" s="19" t="inlineStr">
+      <c r="H214" s="19" t="inlineStr">
         <is>
           <t>dev_form3_landing.png</t>
         </is>
@@ -6729,19 +7605,23 @@
   </sheetData>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A4" r:id="rId1"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G4" r:id="rId2"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A36" r:id="rId3"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E36" r:id="rId4"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I36" r:id="rId5"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M36" r:id="rId6"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q36" r:id="rId7"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A68" r:id="rId8"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E68" r:id="rId9"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I68" r:id="rId10"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M68" r:id="rId11"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q68" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H4" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A34" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H34" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A64" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H64" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A94" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H94" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A124" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H124" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A154" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H154" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A184" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H184" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A214" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H214" r:id="rId16"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId13"/>
+  <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId17"/>
 </worksheet>
 </file>